--- a/isolated_excel/NVIDIA Returns - Current.xlsx
+++ b/isolated_excel/NVIDIA Returns - Current.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Returns" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Returns" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Returns'!$A$1:$H$114</definedName>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.62549090385437</v>
+        <v>2.628551244735718</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.685508012771606</v>
+        <v>2.68863844871521</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.02285938558352174</v>
+        <v>0.02285943791274025</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>2.285938558352174</v>
+        <v>2.285943791274025</v>
       </c>
     </row>
     <row r="3">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.685508012771606</v>
+        <v>2.68863844871521</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.499260902404785</v>
+        <v>2.50217342376709</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.06935265487240272</v>
+        <v>-0.06935295634012228</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-6.935265487240272</v>
+        <v>-6.935295634012228</v>
       </c>
     </row>
     <row r="4">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.499260902404785</v>
+        <v>2.50217342376709</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.682739973068237</v>
+        <v>2.685867547988892</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.07341333211226919</v>
+        <v>0.07341382594706225</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>7.341333211226919</v>
+        <v>7.341382594706225</v>
       </c>
     </row>
     <row r="5">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.682739973068237</v>
+        <v>2.685867547988892</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.568711996078491</v>
+        <v>2.571706056594849</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.04250429714935544</v>
+        <v>-0.04250451273352041</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-4.250429714935544</v>
+        <v>-4.250451273352041</v>
       </c>
     </row>
     <row r="6">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.568711996078491</v>
+        <v>2.571706056594849</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -653,13 +653,13 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3.558810949325562</v>
+        <v>3.562959671020508</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.385445684357997</v>
+        <v>0.3854459229054199</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>38.5445684357997</v>
+        <v>38.54459229054199</v>
       </c>
     </row>
     <row r="7">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.558810949325562</v>
+        <v>3.562959671020508</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.563989400863647</v>
+        <v>3.568142890930176</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.001455107228740982</v>
+        <v>0.001454751214790884</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.1455107228740982</v>
+        <v>0.1454751214790884</v>
       </c>
     </row>
     <row r="8">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.563989400863647</v>
+        <v>3.568142890930176</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -721,13 +721,13 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4.006529331207275</v>
+        <v>4.011197566986084</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1241698222324648</v>
+        <v>0.124169544101528</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12.41698222324647</v>
+        <v>12.4169544101528</v>
       </c>
     </row>
     <row r="9">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4.006529331207275</v>
+        <v>4.011197566986084</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.181060791015625</v>
+        <v>4.185932159423828</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.04356175766614401</v>
+        <v>0.0435617018408383</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>4.356175766614401</v>
+        <v>4.35617018408383</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4.181060791015625</v>
+        <v>4.185932159423828</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4.411284446716309</v>
+        <v>4.416426658630371</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05506345571329518</v>
+        <v>0.05506407902183241</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>5.506345571329518</v>
+        <v>5.506407902183241</v>
       </c>
     </row>
     <row r="11">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.411284446716309</v>
+        <v>4.416426658630371</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -823,13 +823,13 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5.103192329406738</v>
+        <v>5.109140396118164</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1568495278524773</v>
+        <v>0.1568493696446027</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>15.68495278524773</v>
+        <v>15.68493696446027</v>
       </c>
     </row>
     <row r="12">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>5.103192329406738</v>
+        <v>5.109140396118164</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4.956112384796143</v>
+        <v>4.961888313293457</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-0.02882116430593051</v>
+        <v>-0.02882130288229823</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>-2.882116430593051</v>
+        <v>-2.882130288229823</v>
       </c>
     </row>
     <row r="13">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4.956112384796143</v>
+        <v>4.961888313293457</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -891,13 +891,13 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4.778075218200684</v>
+        <v>4.783644199371338</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.03592274605023549</v>
+        <v>-0.03592263724368461</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-3.592274605023549</v>
+        <v>-3.592263724368461</v>
       </c>
     </row>
     <row r="14">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.778075218200684</v>
+        <v>4.783644199371338</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6.069512844085693</v>
+        <v>6.076587677001953</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2702840719136557</v>
+        <v>0.2702842067143147</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>27.02840719136557</v>
+        <v>27.02842067143148</v>
       </c>
     </row>
     <row r="15">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6.069512844085693</v>
+        <v>6.076587677001953</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5.979396343231201</v>
+        <v>5.986364841461182</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.01484740261194184</v>
+        <v>-0.0148476151972986</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>-1.484740261194184</v>
+        <v>-1.48476151972986</v>
       </c>
     </row>
     <row r="16">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.979396343231201</v>
+        <v>5.986364841461182</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5.722183704376221</v>
+        <v>5.728850841522217</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.04301648930600666</v>
+        <v>-0.04301675670607963</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-4.301648930600665</v>
+        <v>-4.301675670607963</v>
       </c>
     </row>
     <row r="17">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5.722183704376221</v>
+        <v>5.728850841522217</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -1027,13 +1027,13 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.556884288787842</v>
+        <v>5.563360691070557</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02888747096007438</v>
+        <v>-0.02888714596166508</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-2.888747096007438</v>
+        <v>-2.888714596166508</v>
       </c>
     </row>
     <row r="18">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5.556884288787842</v>
+        <v>5.563360691070557</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>6.235026359558105</v>
+        <v>6.242292404174805</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1220363850545809</v>
+        <v>0.1220362566450102</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.20363850545809</v>
+        <v>12.20362566450102</v>
       </c>
     </row>
     <row r="19">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6.235026359558105</v>
+        <v>6.242292404174805</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.857002735137939</v>
+        <v>5.863829135894775</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-0.06062903388382113</v>
+        <v>-0.06062889140324723</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>-6.062903388382113</v>
+        <v>-6.062889140324723</v>
       </c>
     </row>
     <row r="20">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.857002735137939</v>
+        <v>5.863829135894775</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6.053802013397217</v>
+        <v>6.060858249664307</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.0336006806140996</v>
+        <v>0.03360075970894849</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3.36006806140996</v>
+        <v>3.360075970894849</v>
       </c>
     </row>
     <row r="21">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.053802013397217</v>
+        <v>6.060858249664307</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>6.943193912506104</v>
+        <v>6.951286315917969</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.1469145996417855</v>
+        <v>0.1469145176432696</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>14.69145996417856</v>
+        <v>14.69145176432696</v>
       </c>
     </row>
     <row r="22">
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.943193912506104</v>
+        <v>6.951286315917969</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -1197,13 +1197,13 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>6.95160436630249</v>
+        <v>6.959707736968994</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.001211323477692039</v>
+        <v>0.001211491034650791</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.1211323477692039</v>
+        <v>0.1211491034650791</v>
       </c>
     </row>
     <row r="23">
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.95160436630249</v>
+        <v>6.959707736968994</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1231,13 +1231,13 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5.215311050415039</v>
+        <v>5.221388339996338</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-0.249768718758512</v>
+        <v>-0.2497690223023227</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>-24.9768718758512</v>
+        <v>-24.97690223023227</v>
       </c>
     </row>
     <row r="24">
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>5.215311050415039</v>
+        <v>5.221388339996338</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -1265,13 +1265,13 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>4.046821117401123</v>
+        <v>4.05153751373291</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-0.2240499026267909</v>
+        <v>-0.2240497641790513</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>-22.40499026267909</v>
+        <v>-22.40497641790513</v>
       </c>
     </row>
     <row r="25">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4.046821117401123</v>
+        <v>4.05153751373291</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.305700540542603</v>
+        <v>3.309553384780884</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-0.1831364805505585</v>
+        <v>-0.1831364331286653</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>-18.31364805505585</v>
+        <v>-18.31364331286654</v>
       </c>
     </row>
     <row r="26">
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3.305700540542603</v>
+        <v>3.309553384780884</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -1333,13 +1333,13 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3.559508323669434</v>
+        <v>3.56365704536438</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.07677881889603055</v>
+        <v>0.07677883721471357</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>7.677881889603055</v>
+        <v>7.677883721471357</v>
       </c>
     </row>
     <row r="27">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.559508323669434</v>
+        <v>3.56365704536438</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -1367,13 +1367,13 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.823691368103027</v>
+        <v>3.828147411346436</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.07421897082719897</v>
+        <v>0.07421880461985131</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>7.421897082719897</v>
+        <v>7.421880461985131</v>
       </c>
     </row>
     <row r="28">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.823691368103027</v>
+        <v>3.828147411346436</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>4.450810432434082</v>
+        <v>4.455998420715332</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1640088082323901</v>
+        <v>0.1640090994165946</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>16.40088082323901</v>
+        <v>16.40090994165946</v>
       </c>
     </row>
     <row r="29">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.450810432434082</v>
+        <v>4.455998420715332</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -1435,13 +1435,13 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.486503124237061</v>
+        <v>4.491733074188232</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.008019369133962062</v>
+        <v>0.008019449312812732</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.8019369133962062</v>
+        <v>0.8019449312812732</v>
       </c>
     </row>
     <row r="30">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.486503124237061</v>
+        <v>4.491733074188232</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.361522197723389</v>
+        <v>3.365440368652344</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.2507478308521132</v>
+        <v>-0.2507479155447004</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-25.07478308521132</v>
+        <v>-25.07479155447004</v>
       </c>
     </row>
     <row r="31">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.361522197723389</v>
+        <v>3.365440368652344</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.075467109680176</v>
+        <v>4.080217838287354</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2123873858219085</v>
+        <v>0.2123875009918048</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>21.23873858219085</v>
+        <v>21.23875009918048</v>
       </c>
     </row>
     <row r="32">
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>4.075467109680176</v>
+        <v>4.080217838287354</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4.186890125274658</v>
+        <v>4.191769123077393</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.02733993738529428</v>
+        <v>0.02733954146841877</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>2.733993738529428</v>
+        <v>2.733954146841877</v>
       </c>
     </row>
     <row r="33">
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>4.186890125274658</v>
+        <v>4.191769123077393</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4.160977363586426</v>
+        <v>4.165826797485352</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.006189023574276975</v>
+        <v>-0.006188872724219974</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>-0.6189023574276975</v>
+        <v>-0.6188872724219974</v>
       </c>
     </row>
     <row r="34">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>4.160977363586426</v>
+        <v>4.165826797485352</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -1605,13 +1605,13 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>4.323929786682129</v>
+        <v>4.328968524932861</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.03916205469458545</v>
+        <v>0.03916190839858924</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>3.916205469458545</v>
+        <v>3.916190839858924</v>
       </c>
     </row>
     <row r="35">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>4.323929786682129</v>
+        <v>4.328968524932861</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -1639,13 +1639,13 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.993372917175293</v>
+        <v>4.999191284179688</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1548228494725041</v>
+        <v>0.1548227378847067</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>15.48228494725041</v>
+        <v>15.48227378847067</v>
       </c>
     </row>
     <row r="36">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>4.993372917175293</v>
+        <v>4.999191284179688</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.387832641601562</v>
+        <v>5.394112586975098</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.07899664835155384</v>
+        <v>0.07899703778992584</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>7.899664835155384</v>
+        <v>7.899703778992584</v>
       </c>
     </row>
     <row r="37">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.387832641601562</v>
+        <v>5.394112586975098</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -1707,13 +1707,13 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.849206924438477</v>
+        <v>5.856024265289307</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.08563263069354887</v>
+        <v>0.08563256158752863</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>8.563263069354887</v>
+        <v>8.563256158752864</v>
       </c>
     </row>
     <row r="38">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>5.849206924438477</v>
+        <v>5.856024265289307</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -1741,13 +1741,13 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>5.877297401428223</v>
+        <v>5.88414478302002</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.00480244199814206</v>
+        <v>0.004801981080815088</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.480244199814206</v>
+        <v>0.4801981080815088</v>
       </c>
     </row>
     <row r="39">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>5.877297401428223</v>
+        <v>5.88414478302002</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>6.717552185058594</v>
+        <v>6.725380897521973</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.1429661843258405</v>
+        <v>0.1429665899672494</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>14.29661843258405</v>
+        <v>14.29665899672494</v>
       </c>
     </row>
     <row r="40">
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>6.717552185058594</v>
+        <v>6.725380897521973</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>6.556620597839355</v>
+        <v>6.564263343811035</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.02395687934917534</v>
+        <v>-0.02395664367059158</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>-2.395687934917534</v>
+        <v>-2.395664367059158</v>
       </c>
     </row>
     <row r="41">
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6.556620597839355</v>
+        <v>6.564263343811035</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -1843,13 +1843,13 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>7.269988536834717</v>
+        <v>7.278463363647461</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1088011618714742</v>
+        <v>0.1088012443178095</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>10.88011618714742</v>
+        <v>10.88012443178095</v>
       </c>
     </row>
     <row r="42">
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>7.269988536834717</v>
+        <v>7.278463363647461</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>8.830545425415039</v>
+        <v>8.840836524963379</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2146574070472709</v>
+        <v>0.214657007015965</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>21.46574070472709</v>
+        <v>21.4657007015965</v>
       </c>
     </row>
     <row r="43">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>8.830545425415039</v>
+        <v>8.840836524963379</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>9.453958511352539</v>
+        <v>9.464973449707031</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.07059734771798643</v>
+        <v>0.07059704395407729</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>7.059734771798643</v>
+        <v>7.059704395407729</v>
       </c>
     </row>
     <row r="44">
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9.453958511352539</v>
+        <v>9.464973449707031</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -1945,13 +1945,13 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.56580352783203</v>
+        <v>10.57811832427979</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1176062931886535</v>
+        <v>0.1176067614439225</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>11.76062931886534</v>
+        <v>11.76067614439225</v>
       </c>
     </row>
     <row r="45">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10.56580352783203</v>
+        <v>10.57811832427979</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -1979,13 +1979,13 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13.31282901763916</v>
+        <v>13.32834720611572</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2599921040147133</v>
+        <v>0.2599922592587551</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>25.99921040147133</v>
+        <v>25.99922592587551</v>
       </c>
     </row>
     <row r="46">
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>13.31282901763916</v>
+        <v>13.32834720611572</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>13.47213935852051</v>
+        <v>13.48784160614014</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.01196667820718389</v>
+        <v>0.01196655500925359</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>1.196667820718389</v>
+        <v>1.196655500925359</v>
       </c>
     </row>
     <row r="47">
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>13.47213935852051</v>
+        <v>13.48784160614014</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -2047,13 +2047,13 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>12.47993659973145</v>
+        <v>12.49448299407959</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>-0.07364849281799779</v>
+        <v>-0.0736484488080239</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>-7.364849281799779</v>
+        <v>-7.364844880802391</v>
       </c>
     </row>
     <row r="48">
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>12.47993659973145</v>
+        <v>12.49448299407959</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.34369564056396</v>
+        <v>13.35924911499023</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06921181321154357</v>
+        <v>0.06921183704202938</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>6.921181321154357</v>
+        <v>6.921183704202938</v>
       </c>
     </row>
     <row r="49">
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>13.34369564056396</v>
+        <v>13.35924911499023</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>13.00252914428711</v>
+        <v>13.01768684387207</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>-0.0255676167582638</v>
+        <v>-0.0255674752509033</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>-2.55676167582638</v>
+        <v>-2.55674752509033</v>
       </c>
     </row>
     <row r="50">
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>13.00252914428711</v>
+        <v>13.01768684387207</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>12.93754482269287</v>
+        <v>12.95262145996094</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-0.004997821644782907</v>
+        <v>-0.00499822930843985</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>-0.4997821644782907</v>
+        <v>-0.499822930843985</v>
       </c>
     </row>
     <row r="51">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>12.93754482269287</v>
+        <v>12.95262145996094</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>13.65937995910645</v>
+        <v>13.67529964447021</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.05579382690504398</v>
+        <v>0.05579397087633686</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>5.579382690504398</v>
+        <v>5.579397087633686</v>
       </c>
     </row>
     <row r="52">
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>13.65937995910645</v>
+        <v>13.67529964447021</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>13.29919147491455</v>
+        <v>13.31469058990479</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-0.02636931436640821</v>
+        <v>-0.02636937134399442</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>-2.636931436640821</v>
+        <v>-2.636937134399442</v>
       </c>
     </row>
     <row r="53">
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>13.29919147491455</v>
+        <v>13.31469058990479</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -2251,13 +2251,13 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14.9543342590332</v>
+        <v>14.97176265716553</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1244543916252838</v>
+        <v>0.1244544179282046</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>12.44543916252838</v>
+        <v>12.44544179282046</v>
       </c>
     </row>
     <row r="54">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>14.9543342590332</v>
+        <v>14.97176265716553</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>16.18479537963867</v>
+        <v>16.20365524291992</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.08228123695056544</v>
+        <v>0.08228106562755366</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>8.228123695056544</v>
+        <v>8.228106562755366</v>
       </c>
     </row>
     <row r="55">
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>16.18479537963867</v>
+        <v>16.20365524291992</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>19.93355178833008</v>
+        <v>19.95678520202637</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2316221070924096</v>
+        <v>0.2316224273375818</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>23.16221070924096</v>
+        <v>23.16224273375818</v>
       </c>
     </row>
     <row r="56">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>19.93355178833008</v>
+        <v>19.95678520202637</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>19.43178939819336</v>
+        <v>19.45443153381348</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.02517175039675923</v>
+        <v>-0.02517207371465235</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>-2.517175039675923</v>
+        <v>-2.517207371465235</v>
       </c>
     </row>
     <row r="57">
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>19.43178939819336</v>
+        <v>19.45443153381348</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>22.3117733001709</v>
+        <v>22.33777809143066</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1482099174173481</v>
+        <v>0.1482102703749366</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>14.82099174173481</v>
+        <v>14.82102703749366</v>
       </c>
     </row>
     <row r="58">
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>22.3117733001709</v>
+        <v>22.33777809143066</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -2421,13 +2421,13 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>20.64823341369629</v>
+        <v>20.67229652404785</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-0.0745588377980636</v>
+        <v>-0.07455896287293373</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>-7.45588377980636</v>
+        <v>-7.455896287293373</v>
       </c>
     </row>
     <row r="59">
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>20.64823341369629</v>
+        <v>20.67229652404785</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25.48336219787598</v>
+        <v>25.51306533813477</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2341667050786278</v>
+        <v>0.2341669590727717</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>23.41667050786278</v>
+        <v>23.41669590727717</v>
       </c>
     </row>
     <row r="60">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>25.48336219787598</v>
+        <v>25.51306533813477</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>32.5691032409668</v>
+        <v>32.60707092285156</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2780536174179329</v>
+        <v>0.2780538320541703</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>27.80536174179329</v>
+        <v>27.80538320541703</v>
       </c>
     </row>
     <row r="61">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>32.5691032409668</v>
+        <v>32.60707092285156</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>29.31837844848633</v>
+        <v>29.35254859924316</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-0.0998100797688396</v>
+        <v>-0.09981032430998205</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>-9.98100797688396</v>
+        <v>-9.981032430998205</v>
       </c>
     </row>
     <row r="62">
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>29.31837844848633</v>
+        <v>29.35254859924316</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -2557,13 +2557,13 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>24.40888786315918</v>
+        <v>24.43733787536621</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-0.1674543697549078</v>
+        <v>-0.1674543083459433</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>-16.74543697549078</v>
+        <v>-16.74543083459433</v>
       </c>
     </row>
     <row r="63">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>24.40888786315918</v>
+        <v>24.43733787536621</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>24.30820274353027</v>
+        <v>24.33654022216797</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-0.004124936793243772</v>
+        <v>-0.004124739515913078</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>-0.4124936793243772</v>
+        <v>-0.4124739515913078</v>
       </c>
     </row>
     <row r="64">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>24.30820274353027</v>
+        <v>24.33654022216797</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -2625,13 +2625,13 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>27.20470237731934</v>
+        <v>27.23641204833984</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1191572928837767</v>
+        <v>0.1191571110642262</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>11.91572928837767</v>
+        <v>11.91571110642262</v>
       </c>
     </row>
     <row r="65">
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>27.20470237731934</v>
+        <v>27.23641204833984</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -2659,13 +2659,13 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>18.49174499511719</v>
+        <v>18.51329612731934</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-0.3202739460758143</v>
+        <v>-0.3202740473135195</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>-32.02739460758143</v>
+        <v>-32.02740473135195</v>
       </c>
     </row>
     <row r="66">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>18.49174499511719</v>
+        <v>18.51329612731934</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18.61636543273926</v>
+        <v>18.63806915283203</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.006739247034553975</v>
+        <v>0.006739644018796564</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.6739247034553975</v>
+        <v>0.6739644018796564</v>
       </c>
     </row>
     <row r="67">
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>18.61636543273926</v>
+        <v>18.63806915283203</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>15.11703205108643</v>
+        <v>15.13465309143066</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.187970814942148</v>
+        <v>-0.1879709766432016</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>-18.79708149421479</v>
+        <v>-18.79709766432016</v>
       </c>
     </row>
     <row r="68">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>15.11703205108643</v>
+        <v>15.13465309143066</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.11271286010742</v>
+        <v>18.13382720947266</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1981659362034429</v>
+        <v>0.1981660299660348</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>19.81659362034429</v>
+        <v>19.81660299660348</v>
       </c>
     </row>
     <row r="69">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>18.11271286010742</v>
+        <v>18.13382720947266</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -2795,13 +2795,13 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>15.05221176147461</v>
+        <v>15.0697546005249</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.1689697795283583</v>
+        <v>-0.1689699903695542</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>-16.89697795283583</v>
+        <v>-16.89699903695542</v>
       </c>
     </row>
     <row r="70">
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>15.05221176147461</v>
+        <v>15.0697546005249</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -2829,13 +2829,13 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>12.10898971557617</v>
+        <v>12.12310409545898</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-0.1955341907580299</v>
+        <v>-0.1955340735915687</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>-19.55341907580299</v>
+        <v>-19.55340735915687</v>
       </c>
     </row>
     <row r="71">
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>12.10898971557617</v>
+        <v>12.12310409545898</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -2863,13 +2863,13 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>13.46363162994385</v>
+        <v>13.47932434082031</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1118707626471229</v>
+        <v>0.1118707085810915</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>11.18707626471229</v>
+        <v>11.18707085810915</v>
       </c>
     </row>
     <row r="72">
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>13.46363162994385</v>
+        <v>13.47932434082031</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -2897,13 +2897,13 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>16.88547897338867</v>
+        <v>16.90515899658203</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2541548549081252</v>
+        <v>0.2541547757988909</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>25.41548549081252</v>
+        <v>25.41547757988909</v>
       </c>
     </row>
     <row r="73">
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>16.88547897338867</v>
+        <v>16.90515899658203</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
@@ -2931,13 +2931,13 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>14.5816011428833</v>
+        <v>14.59859466552734</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>-0.1364413668179776</v>
+        <v>-0.1364414455682458</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>-13.64413668179776</v>
+        <v>-13.64414455682458</v>
       </c>
     </row>
     <row r="74">
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>14.5816011428833</v>
+        <v>14.59859466552734</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
@@ -2965,13 +2965,13 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>19.49368858337402</v>
+        <v>19.51640510559082</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.3368688659330197</v>
+        <v>0.3368687570781206</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>33.68688659330197</v>
+        <v>33.68687570781206</v>
       </c>
     </row>
     <row r="75">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>19.49368858337402</v>
+        <v>19.51640510559082</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -2999,13 +2999,13 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>23.16452789306641</v>
+        <v>23.19152641296387</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1883091183073071</v>
+        <v>0.1883093370674214</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>18.83091183073071</v>
+        <v>18.83093370674214</v>
       </c>
     </row>
     <row r="76">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>23.16452789306641</v>
+        <v>23.19152641296387</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -3033,13 +3033,13 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>27.72012329101562</v>
+        <v>27.75243186950684</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1966625617832167</v>
+        <v>0.1966625816398813</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>19.66625617832167</v>
+        <v>19.66625816398813</v>
       </c>
     </row>
     <row r="77">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>27.72012329101562</v>
+        <v>27.75243186950684</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>27.69218254089355</v>
+        <v>27.72445487976074</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>-0.001007959085489563</v>
+        <v>-0.001008091466637717</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>-0.1007959085489563</v>
+        <v>-0.1008091466637717</v>
       </c>
     </row>
     <row r="78">
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>27.69218254089355</v>
+        <v>27.72445487976074</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -3101,13 +3101,13 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>37.75653457641602</v>
+        <v>37.80053329467773</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.3634365771155903</v>
+        <v>0.3634364844544762</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>36.34365771155903</v>
+        <v>36.34364844544762</v>
       </c>
     </row>
     <row r="79">
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>37.75653457641602</v>
+        <v>37.80053329467773</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>42.21975708007812</v>
+        <v>42.26895141601562</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.1182105972842642</v>
+        <v>0.118210451860663</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>11.82105972842642</v>
+        <v>11.8210451860663</v>
       </c>
     </row>
     <row r="80">
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>42.21975708007812</v>
+        <v>42.26895141601562</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -3169,13 +3169,13 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>46.63813781738281</v>
+        <v>46.69250106811523</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.1046519696672901</v>
+        <v>0.1046524577475925</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>10.46519696672901</v>
+        <v>10.46524577475925</v>
       </c>
     </row>
     <row r="81">
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>46.63813781738281</v>
+        <v>46.69250106811523</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
@@ -3203,13 +3203,13 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>49.25904083251953</v>
+        <v>49.31644821166992</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05619656225124547</v>
+        <v>0.05619632882219916</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>5.619656225124547</v>
+        <v>5.619632882219916</v>
       </c>
     </row>
     <row r="82">
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>49.25904083251953</v>
+        <v>49.31644821166992</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>43.41799926757812</v>
+        <v>43.46859741210938</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-0.1185780613309324</v>
+        <v>-0.1185781014573704</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>-11.85780613309324</v>
+        <v>-11.85781014573704</v>
       </c>
     </row>
     <row r="83">
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>43.41799926757812</v>
+        <v>43.46859741210938</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -3271,13 +3271,13 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>40.70405578613281</v>
+        <v>40.75150299072266</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>-0.06250733629432614</v>
+        <v>-0.06250706448213572</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>-6.250733629432615</v>
+        <v>-6.250706448213572</v>
       </c>
     </row>
     <row r="84">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>40.70405578613281</v>
+        <v>40.75150299072266</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
@@ -3305,13 +3305,13 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>46.68291473388672</v>
+        <v>46.73731994628906</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.1468860739373987</v>
+        <v>0.146885796014177</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>14.68860739373987</v>
+        <v>14.6885796014177</v>
       </c>
     </row>
     <row r="85">
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>46.68291473388672</v>
+        <v>46.73731994628906</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -3339,13 +3339,13 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>49.43412780761719</v>
+        <v>49.49174499511719</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05893404662955604</v>
+        <v>0.05893416764148074</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>5.893404662955604</v>
+        <v>5.893416764148074</v>
       </c>
     </row>
     <row r="86">
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>49.43412780761719</v>
+        <v>49.49174499511719</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -3373,13 +3373,13 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>61.41783142089844</v>
+        <v>61.48941421508789</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.242417620068432</v>
+        <v>0.2424175834001081</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>24.2417620068432</v>
+        <v>24.24175834001081</v>
       </c>
     </row>
     <row r="87">
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>61.41783142089844</v>
+        <v>61.48941421508789</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -3407,13 +3407,13 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>78.97163391113281</v>
+        <v>79.06366729736328</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.2858095456014653</v>
+        <v>0.2858094081170013</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>28.58095456014653</v>
+        <v>28.58094081170013</v>
       </c>
     </row>
     <row r="88">
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>78.97163391113281</v>
+        <v>79.06366729736328</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
@@ -3441,13 +3441,13 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>90.19991302490234</v>
+        <v>90.30503845214844</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.1421811675620739</v>
+        <v>0.1421812513768894</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>14.21811675620739</v>
+        <v>14.21812513768894</v>
       </c>
     </row>
     <row r="89">
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>90.19991302490234</v>
+        <v>90.30503845214844</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -3475,13 +3475,13 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>86.25274658203125</v>
+        <v>86.35327911376953</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>-0.04376020231617472</v>
+        <v>-0.04376012021159703</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>-4.376020231617472</v>
+        <v>-4.376012021159703</v>
       </c>
     </row>
     <row r="90">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>86.25274658203125</v>
+        <v>86.35327911376953</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>109.4436187744141</v>
+        <v>109.571174621582</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.2688711155456016</v>
+        <v>0.2688710347319083</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>26.88711155456016</v>
+        <v>26.88710347319083</v>
       </c>
     </row>
     <row r="91">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>109.4436187744141</v>
+        <v>109.571174621582</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -3543,13 +3543,13 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>123.3367156982422</v>
+        <v>123.4804611206055</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.1269429600319107</v>
+        <v>0.1269429350106077</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>12.69429600319107</v>
+        <v>12.69429350106077</v>
       </c>
     </row>
     <row r="92">
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>123.3367156982422</v>
+        <v>123.4804611206055</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -3577,13 +3577,13 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>116.8274459838867</v>
+        <v>116.9635848999023</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-0.05277641517778997</v>
+        <v>-0.0527765782664027</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>-5.277641517778997</v>
+        <v>-5.27765782664027</v>
       </c>
     </row>
     <row r="93">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>116.8274459838867</v>
+        <v>116.9635848999023</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
@@ -3611,13 +3611,13 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>119.1735687255859</v>
+        <v>119.3124694824219</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.0200819483978345</v>
+        <v>0.02008218698605813</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>2.00819483978345</v>
+        <v>2.008218698605813</v>
       </c>
     </row>
     <row r="94">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>119.1735687255859</v>
+        <v>119.3124694824219</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -3645,13 +3645,13 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>121.2505416870117</v>
+        <v>121.3918609619141</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.01742813430558843</v>
+        <v>0.0174281153387621</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>1.742813430558843</v>
+        <v>1.74281153387621</v>
       </c>
     </row>
     <row r="95">
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>121.2505416870117</v>
+        <v>121.3918609619141</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>132.5528717041016</v>
+        <v>132.7073822021484</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.09321467648585813</v>
+        <v>0.09321482635301681</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>9.321467648585813</v>
+        <v>9.321482635301681</v>
       </c>
     </row>
     <row r="96">
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>132.5528717041016</v>
+        <v>132.7073822021484</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -3713,13 +3713,13 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>138.0343322753906</v>
+        <v>138.1952056884766</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.04135301258146518</v>
+        <v>0.04135281244542011</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>4.135301258146518</v>
+        <v>4.135281244542011</v>
       </c>
     </row>
     <row r="97">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>138.0343322753906</v>
+        <v>138.1952056884766</v>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
@@ -3747,13 +3747,13 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>134.0897369384766</v>
+        <v>134.2460174560547</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>-0.02857691468412549</v>
+        <v>-0.02857688306006967</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>-2.857691468412549</v>
+        <v>-2.857688306006967</v>
       </c>
     </row>
     <row r="98">
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>134.0897369384766</v>
+        <v>134.2460174560547</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -3781,13 +3781,13 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>119.8909454345703</v>
+        <v>120.0306701660156</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-0.1058902182082808</v>
+        <v>-0.1058902719009333</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>-10.58902182082808</v>
+        <v>-10.58902719009333</v>
       </c>
     </row>
     <row r="99">
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>119.8909454345703</v>
+        <v>120.0306701660156</v>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
@@ -3815,13 +3815,13 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>124.7337112426758</v>
+        <v>124.8790817260742</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.04039309049196182</v>
+        <v>0.0403931058066469</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>4.039309049196182</v>
+        <v>4.03931058066469</v>
       </c>
     </row>
     <row r="100">
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>124.7337112426758</v>
+        <v>124.8790817260742</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -3849,13 +3849,13 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>108.2283172607422</v>
+        <v>108.3544616699219</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-0.1323250452303268</v>
+        <v>-0.1323249644996555</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>-13.23250452303268</v>
+        <v>-13.23249644996555</v>
       </c>
     </row>
     <row r="101">
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>108.2283172607422</v>
+        <v>108.3544616699219</v>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
@@ -3883,13 +3883,13 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>108.7675628662109</v>
+        <v>108.8943328857422</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.004982481656530036</v>
+        <v>0.004982454875415376</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0.4982481656530036</v>
+        <v>0.4982454875415376</v>
       </c>
     </row>
     <row r="102">
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>108.7675628662109</v>
+        <v>108.8943328857422</v>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
@@ -3917,13 +3917,13 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>134.9409027099609</v>
+        <v>135.0981750488281</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.2406355273027898</v>
+        <v>0.2406354992833322</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>24.06355273027898</v>
+        <v>24.06354992833322</v>
       </c>
     </row>
     <row r="103">
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>134.9409027099609</v>
+        <v>135.0981750488281</v>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
@@ -3951,13 +3951,13 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>157.7798614501953</v>
+        <v>157.9637603759766</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.1692515633256428</v>
+        <v>0.1692516225247618</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>16.92515633256428</v>
+        <v>16.92516225247618</v>
       </c>
     </row>
     <row r="104">
@@ -3977,7 +3977,7 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>157.7798614501953</v>
+        <v>157.9637603759766</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>177.6334075927734</v>
+        <v>177.8404388427734</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.1258306729394936</v>
+        <v>0.1258306235524371</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>12.58306729394936</v>
+        <v>12.58306235524371</v>
       </c>
     </row>
     <row r="105">
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>177.6334075927734</v>
+        <v>177.8404388427734</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -4019,13 +4019,13 @@
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>173.9483032226562</v>
+        <v>174.1510467529297</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>-0.02074555918313137</v>
+        <v>-0.02074551836382665</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>-2.074555918313137</v>
+        <v>-2.074551836382665</v>
       </c>
     </row>
     <row r="106">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>173.9483032226562</v>
+        <v>174.1510467529297</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
@@ -4053,13 +4053,13 @@
         </is>
       </c>
       <c r="F106" s="3" t="n">
-        <v>186.3423309326172</v>
+        <v>186.5595092773438</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.07125121360969189</v>
+        <v>0.07125115097366086</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>7.125121360969189</v>
+        <v>7.125115097366086</v>
       </c>
     </row>
     <row r="107">
@@ -4079,7 +4079,7 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>186.3423309326172</v>
+        <v>186.5595092773438</v>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
@@ -4087,13 +4087,13 @@
         </is>
       </c>
       <c r="F107" s="3" t="n">
-        <v>202.2320709228516</v>
+        <v>202.4677734375</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0.0852717678839181</v>
+        <v>0.08527179462348733</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>8.527176788391809</v>
+        <v>8.527179462348734</v>
       </c>
     </row>
     <row r="108">
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>202.2320709228516</v>
+        <v>202.4677734375</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
@@ -4121,13 +4121,13 @@
         </is>
       </c>
       <c r="F108" s="3" t="n">
-        <v>176.7745361328125</v>
+        <v>176.9805603027344</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>-0.125882777513319</v>
+        <v>-0.1258828143464189</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>-12.5882777513319</v>
+        <v>-12.58828143464189</v>
       </c>
     </row>
     <row r="109">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>176.7745361328125</v>
+        <v>176.9805603027344</v>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
@@ -4155,13 +4155,13 @@
         </is>
       </c>
       <c r="F109" s="3" t="n">
-        <v>186.2728118896484</v>
+        <v>186.4899139404297</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>0.05373101785259271</v>
+        <v>0.0537310630129606</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>5.373101785259271</v>
+        <v>5.37310630129606</v>
       </c>
     </row>
     <row r="110">
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>186.2728118896484</v>
+        <v>186.4899139404297</v>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
@@ -4189,13 +4189,13 @@
         </is>
       </c>
       <c r="F110" s="3" t="n">
-        <v>190.8971710205078</v>
+        <v>191.1196594238281</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0.02482573320254033</v>
+        <v>0.02482571515839349</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>2.482573320254033</v>
+        <v>2.482571515839349</v>
       </c>
     </row>
     <row r="111">
@@ -4215,7 +4215,7 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>190.8971710205078</v>
+        <v>191.1196594238281</v>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="F111" s="3" t="n">
-        <v>176.9741516113281</v>
+        <v>177.180419921875</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>-0.07293465552553402</v>
+        <v>-0.07293461878268304</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>-7.293465552553402</v>
+        <v>-7.293461878268303</v>
       </c>
     </row>
     <row r="112">
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>176.9741516113281</v>
+        <v>177.180419921875</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -4257,13 +4257,13 @@
         </is>
       </c>
       <c r="F112" s="3" t="n">
-        <v>174.1969757080078</v>
+        <v>174.3999938964844</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>-0.0156925510196515</v>
+        <v>-0.01569262578007558</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>-1.56925510196515</v>
+        <v>-1.569262578007558</v>
       </c>
     </row>
     <row r="113">
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>174.1969757080078</v>
+        <v>174.3999938964844</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -4291,13 +4291,13 @@
         </is>
       </c>
       <c r="F113" s="3" t="n">
-        <v>199.3376770019531</v>
+        <v>199.5700073242188</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0.1443234085538123</v>
+        <v>0.1443234765402235</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>14.43234085538123</v>
+        <v>14.43234765402235</v>
       </c>
     </row>
     <row r="114">
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>199.3376770019531</v>
+        <v>199.5700073242188</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -4325,13 +4325,13 @@
         </is>
       </c>
       <c r="F114" s="3" t="n">
-        <v>210.8942108154297</v>
+        <v>211.1399993896484</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0.05797465881657349</v>
+        <v>0.05797460360179896</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>5.797465881657349</v>
+        <v>5.797460360179896</v>
       </c>
     </row>
   </sheetData>

--- a/isolated_excel/NVIDIA Returns - Current.xlsx
+++ b/isolated_excel/NVIDIA Returns - Current.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Returns" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Returns" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Returns'!$A$1:$H$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Returns'!$A$1:$H$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Source and Method'!$A$1:$B$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:H115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.628551244735718</v>
+        <v>2.625491857528687</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.68863844871521</v>
+        <v>2.685507774353027</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.02285943791274025</v>
+        <v>0.0228589232346097</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>2.285943791274025</v>
+        <v>2.28589232346097</v>
       </c>
     </row>
     <row r="3">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.68863844871521</v>
+        <v>2.685507774353027</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.50217342376709</v>
+        <v>2.499260902404785</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.06935295634012228</v>
+        <v>-0.06935257224980906</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-6.935295634012228</v>
+        <v>-6.935257224980907</v>
       </c>
     </row>
     <row r="4">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.50217342376709</v>
+        <v>2.499260902404785</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.685867547988892</v>
+        <v>2.682740211486816</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.07341382594706225</v>
+        <v>0.07341342750790347</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>7.341382594706225</v>
+        <v>7.341342750790347</v>
       </c>
     </row>
     <row r="5">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.685867547988892</v>
+        <v>2.682740211486816</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.571706056594849</v>
+        <v>2.568711996078491</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.04250451273352041</v>
+        <v>-0.04250438224323216</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-4.250451273352041</v>
+        <v>-4.250438224323217</v>
       </c>
     </row>
     <row r="6">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.571706056594849</v>
+        <v>2.568711996078491</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -653,13 +653,13 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3.562959671020508</v>
+        <v>3.558811664581299</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3854459229054199</v>
+        <v>0.3854459628071725</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>38.54459229054199</v>
+        <v>38.54459628071724</v>
       </c>
     </row>
     <row r="7">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.562959671020508</v>
+        <v>3.558811664581299</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.568142890930176</v>
+        <v>3.563989877700806</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.001454751214790884</v>
+        <v>0.001455039942417358</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.1454751214790884</v>
+        <v>0.1455039942417358</v>
       </c>
     </row>
     <row r="8">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.568142890930176</v>
+        <v>3.563989877700806</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -721,13 +721,13 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4.011197566986084</v>
+        <v>4.006530284881592</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.124169544101528</v>
+        <v>0.1241699394124758</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12.4169544101528</v>
+        <v>12.41699394124758</v>
       </c>
     </row>
     <row r="9">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4.011197566986084</v>
+        <v>4.006530284881592</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.185932159423828</v>
+        <v>4.181059837341309</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.0435617018408383</v>
+        <v>0.04356127123718334</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>4.35617018408383</v>
+        <v>4.356127123718334</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4.185932159423828</v>
+        <v>4.181059837341309</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4.416426658630371</v>
+        <v>4.411284923553467</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05506407902183241</v>
+        <v>0.05506381041381037</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>5.506407902183241</v>
+        <v>5.506381041381037</v>
       </c>
     </row>
     <row r="11">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.416426658630371</v>
+        <v>4.411284923553467</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -823,13 +823,13 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5.109140396118164</v>
+        <v>5.103193759918213</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1568493696446027</v>
+        <v>0.1568497270875411</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>15.68493696446027</v>
+        <v>15.68497270875411</v>
       </c>
     </row>
     <row r="12">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>5.109140396118164</v>
+        <v>5.103193759918213</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4.961888313293457</v>
+        <v>4.956112861633301</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-0.02882130288229823</v>
+        <v>-0.02882134310480688</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>-2.882130288229823</v>
+        <v>-2.882134310480688</v>
       </c>
     </row>
     <row r="13">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4.961888313293457</v>
+        <v>4.956112861633301</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -891,13 +891,13 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4.783644199371338</v>
+        <v>4.778075695037842</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.03592263724368461</v>
+        <v>-0.03592274259403894</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-3.592263724368461</v>
+        <v>-3.592274259403894</v>
       </c>
     </row>
     <row r="14">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.783644199371338</v>
+        <v>4.778075695037842</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6.076587677001953</v>
+        <v>6.069513320922852</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2702842067143147</v>
+        <v>0.2702840449401422</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>27.02842067143148</v>
+        <v>27.02840449401423</v>
       </c>
     </row>
     <row r="15">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6.076587677001953</v>
+        <v>6.069513320922852</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5.986364841461182</v>
+        <v>5.979395389556885</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.0148476151972986</v>
+        <v>-0.01484763713349335</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>-1.48476151972986</v>
+        <v>-1.484763713349335</v>
       </c>
     </row>
     <row r="16">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.986364841461182</v>
+        <v>5.979395389556885</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5.728850841522217</v>
+        <v>5.722182273864746</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.04301675670607963</v>
+        <v>-0.04301657591357244</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-4.301675670607963</v>
+        <v>-4.301657591357245</v>
       </c>
     </row>
     <row r="17">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5.728850841522217</v>
+        <v>5.722182273864746</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -1027,13 +1027,13 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.563360691070557</v>
+        <v>5.556882858276367</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02888714596166508</v>
+        <v>-0.02888747818176995</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-2.888714596166508</v>
+        <v>-2.888747818176995</v>
       </c>
     </row>
     <row r="18">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5.563360691070557</v>
+        <v>5.556882858276367</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>6.242292404174805</v>
+        <v>6.235024929046631</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1220362566450102</v>
+        <v>0.1220364164704759</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.20362566450102</v>
+        <v>12.20364164704759</v>
       </c>
     </row>
     <row r="19">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6.242292404174805</v>
+        <v>6.235024929046631</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.863829135894775</v>
+        <v>5.857002735137939</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-0.06062889140324723</v>
+        <v>-0.06062881836247813</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>-6.062889140324723</v>
+        <v>-6.062881836247813</v>
       </c>
     </row>
     <row r="20">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.863829135894775</v>
+        <v>5.857002735137939</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6.060858249664307</v>
+        <v>6.053802967071533</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.03360075970894849</v>
+        <v>0.03360084344043912</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3.360075970894849</v>
+        <v>3.360084344043912</v>
       </c>
     </row>
     <row r="21">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.060858249664307</v>
+        <v>6.053802967071533</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>6.951286315917969</v>
+        <v>6.943196773529053</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.1469145176432696</v>
+        <v>0.1469148915640635</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>14.69145176432696</v>
+        <v>14.69148915640634</v>
       </c>
     </row>
     <row r="22">
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.951286315917969</v>
+        <v>6.943196773529053</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -1197,13 +1197,13 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>6.959707736968994</v>
+        <v>6.95160436630249</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.001211491034650791</v>
+        <v>0.001210910917214925</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.1211491034650791</v>
+        <v>0.1210910917214925</v>
       </c>
     </row>
     <row r="23">
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.959707736968994</v>
+        <v>6.95160436630249</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1231,13 +1231,13 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5.221388339996338</v>
+        <v>5.215312957763672</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-0.2497690223023227</v>
+        <v>-0.2497684443831978</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>-24.97690223023227</v>
+        <v>-24.97684443831978</v>
       </c>
     </row>
     <row r="24">
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>5.221388339996338</v>
+        <v>5.215312957763672</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -1265,13 +1265,13 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>4.05153751373291</v>
+        <v>4.046821117401123</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-0.2240497641790513</v>
+        <v>-0.2240501864079119</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>-22.40497641790513</v>
+        <v>-22.40501864079118</v>
       </c>
     </row>
     <row r="25">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4.05153751373291</v>
+        <v>4.046821117401123</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.309553384780884</v>
+        <v>3.305699586868286</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-0.1831364331286653</v>
+        <v>-0.1831367162106703</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>-18.31364331286654</v>
+        <v>-18.31367162106703</v>
       </c>
     </row>
     <row r="26">
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3.309553384780884</v>
+        <v>3.305699586868286</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -1333,13 +1333,13 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3.56365704536438</v>
+        <v>3.559508562088013</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.07677883721471357</v>
+        <v>0.07677920166368679</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>7.677883721471357</v>
+        <v>7.677920166368679</v>
       </c>
     </row>
     <row r="27">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.56365704536438</v>
+        <v>3.559508562088013</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -1367,13 +1367,13 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.828147411346436</v>
+        <v>3.823691844940186</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.07421880461985131</v>
+        <v>0.07421903283671338</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>7.421880461985131</v>
+        <v>7.421903283671338</v>
       </c>
     </row>
     <row r="28">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.828147411346436</v>
+        <v>3.823691844940186</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>4.455998420715332</v>
+        <v>4.450812339782715</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1640090994165946</v>
+        <v>0.1640091618973911</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>16.40090994165946</v>
+        <v>16.40091618973911</v>
       </c>
     </row>
     <row r="29">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.455998420715332</v>
+        <v>4.450812339782715</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -1435,13 +1435,13 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.491733074188232</v>
+        <v>4.486504554748535</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.008019449312812732</v>
+        <v>0.008019258562485865</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.8019449312812732</v>
+        <v>0.8019258562485865</v>
       </c>
     </row>
     <row r="30">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.491733074188232</v>
+        <v>4.486504554748535</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.365440368652344</v>
+        <v>3.361522197723389</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.2507479155447004</v>
+        <v>-0.2507480697494133</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-25.07479155447004</v>
+        <v>-25.07480697494133</v>
       </c>
     </row>
     <row r="31">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.365440368652344</v>
+        <v>3.361522197723389</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.080217838287354</v>
+        <v>4.075467586517334</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2123875009918048</v>
+        <v>0.2123875276734657</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>21.23875009918048</v>
+        <v>21.23875276734657</v>
       </c>
     </row>
     <row r="32">
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>4.080217838287354</v>
+        <v>4.075467586517334</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4.191769123077393</v>
+        <v>4.186891078948975</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.02733954146841877</v>
+        <v>0.02734005118829974</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>2.733954146841877</v>
+        <v>2.734005118829974</v>
       </c>
     </row>
     <row r="33">
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>4.191769123077393</v>
+        <v>4.186891078948975</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4.165826797485352</v>
+        <v>4.160977840423584</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.006188872724219974</v>
+        <v>-0.006189136052685562</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>-0.6188872724219974</v>
+        <v>-0.6189136052685562</v>
       </c>
     </row>
     <row r="34">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>4.165826797485352</v>
+        <v>4.160977840423584</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -1605,13 +1605,13 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>4.328968524932861</v>
+        <v>4.323929786682129</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.03916190839858924</v>
+        <v>0.03916193560933667</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>3.916190839858924</v>
+        <v>3.916193560933667</v>
       </c>
     </row>
     <row r="35">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>4.328968524932861</v>
+        <v>4.323929786682129</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -1639,13 +1639,13 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.999191284179688</v>
+        <v>4.993370532989502</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1548227378847067</v>
+        <v>0.1548222980792326</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>15.48227378847067</v>
+        <v>15.48222980792326</v>
       </c>
     </row>
     <row r="36">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>4.999191284179688</v>
+        <v>4.993370532989502</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.394112586975098</v>
+        <v>5.387831687927246</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.07899703778992584</v>
+        <v>0.0789969725522417</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>7.899703778992584</v>
+        <v>7.89969725522417</v>
       </c>
     </row>
     <row r="37">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.394112586975098</v>
+        <v>5.387831687927246</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -1707,13 +1707,13 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.856024265289307</v>
+        <v>5.849206447601318</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.08563256158752863</v>
+        <v>0.08563273435357965</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>8.563256158752864</v>
+        <v>8.563273435357965</v>
       </c>
     </row>
     <row r="38">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>5.856024265289307</v>
+        <v>5.849206447601318</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -1741,13 +1741,13 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>5.88414478302002</v>
+        <v>5.87729549407959</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.004801981080815088</v>
+        <v>0.00480219782459379</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.4801981080815088</v>
+        <v>0.480219782459379</v>
       </c>
     </row>
     <row r="39">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>5.88414478302002</v>
+        <v>5.87729549407959</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>6.725380897521973</v>
+        <v>6.717551231384277</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.1429665899672494</v>
+        <v>0.1429663929865543</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>14.29665899672494</v>
+        <v>14.29663929865543</v>
       </c>
     </row>
     <row r="40">
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>6.725380897521973</v>
+        <v>6.717551231384277</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>6.564263343811035</v>
+        <v>6.556621551513672</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.02395664367059158</v>
+        <v>-0.02395659881516721</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>-2.395664367059158</v>
+        <v>-2.395659881516721</v>
       </c>
     </row>
     <row r="41">
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6.564263343811035</v>
+        <v>6.556621551513672</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -1843,13 +1843,13 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>7.278463363647461</v>
+        <v>7.269989013671875</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1088012443178095</v>
+        <v>0.1088010733200719</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>10.88012443178095</v>
+        <v>10.88010733200719</v>
       </c>
     </row>
     <row r="42">
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>7.278463363647461</v>
+        <v>7.269989013671875</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>8.840836524963379</v>
+        <v>8.830546379089355</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.214657007015965</v>
+        <v>0.2146574585577379</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>21.4657007015965</v>
+        <v>21.46574585577379</v>
       </c>
     </row>
     <row r="43">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>8.840836524963379</v>
+        <v>8.830546379089355</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>9.464973449707031</v>
+        <v>9.45395565032959</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.07059704395407729</v>
+        <v>0.07059690810485542</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>7.059704395407729</v>
+        <v>7.059690810485542</v>
       </c>
     </row>
     <row r="44">
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9.464973449707031</v>
+        <v>9.45395565032959</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -1945,13 +1945,13 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.57811832427979</v>
+        <v>10.5658016204834</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1176067614439225</v>
+        <v>0.1176064296551937</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>11.76067614439225</v>
+        <v>11.76064296551937</v>
       </c>
     </row>
     <row r="45">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10.57811832427979</v>
+        <v>10.5658016204834</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -1979,13 +1979,13 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13.32834720611572</v>
+        <v>13.31282997131348</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2599922592587551</v>
+        <v>0.2599924217301743</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>25.99922592587551</v>
+        <v>25.99924217301744</v>
       </c>
     </row>
     <row r="46">
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>13.32834720611572</v>
+        <v>13.31282997131348</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>13.48784160614014</v>
+        <v>13.47214126586914</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.01196655500925359</v>
+        <v>0.01196674898567385</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>1.196655500925359</v>
+        <v>1.196674898567385</v>
       </c>
     </row>
     <row r="47">
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>13.48784160614014</v>
+        <v>13.47214126586914</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -2047,13 +2047,13 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>12.49448299407959</v>
+        <v>12.47993946075439</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>-0.0736484488080239</v>
+        <v>-0.07364841160242508</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>-7.364844880802391</v>
+        <v>-7.364841160242507</v>
       </c>
     </row>
     <row r="48">
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>12.49448299407959</v>
+        <v>12.47993946075439</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.35924911499023</v>
+        <v>13.34369659423828</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06921183704202938</v>
+        <v>0.06921164451158912</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>6.921183704202938</v>
+        <v>6.921164451158912</v>
       </c>
     </row>
     <row r="49">
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>13.35924911499023</v>
+        <v>13.34369659423828</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>13.01768684387207</v>
+        <v>13.00253200531006</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>-0.0255674752509033</v>
+        <v>-0.02556747199089759</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>-2.55674752509033</v>
+        <v>-2.556747199089759</v>
       </c>
     </row>
     <row r="50">
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>13.01768684387207</v>
+        <v>13.00253200531006</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>12.95262145996094</v>
+        <v>12.93754100799561</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-0.00499822930843985</v>
+        <v>-0.004998333962024648</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>-0.499822930843985</v>
+        <v>-0.4998333962024648</v>
       </c>
     </row>
     <row r="51">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>12.95262145996094</v>
+        <v>12.93754100799561</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>13.67529964447021</v>
+        <v>13.65938282012939</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.05579397087633686</v>
+        <v>0.05579435935218902</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>5.579397087633686</v>
+        <v>5.579435935218902</v>
       </c>
     </row>
     <row r="52">
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>13.67529964447021</v>
+        <v>13.65938282012939</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>13.31469058990479</v>
+        <v>13.29919052124023</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-0.02636937134399442</v>
+        <v>-0.02636958811626222</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>-2.636937134399442</v>
+        <v>-2.636958811626222</v>
       </c>
     </row>
     <row r="53">
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>13.31469058990479</v>
+        <v>13.29919052124023</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -2251,13 +2251,13 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14.97176265716553</v>
+        <v>14.95433521270752</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1244544179282046</v>
+        <v>0.1244545439682092</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>12.44544179282046</v>
+        <v>12.44545439682092</v>
       </c>
     </row>
     <row r="54">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>14.97176265716553</v>
+        <v>14.95433521270752</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>16.20365524291992</v>
+        <v>16.18479537963867</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.08228106562755366</v>
+        <v>0.08228116793085949</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>8.228106562755366</v>
+        <v>8.228116793085949</v>
       </c>
     </row>
     <row r="55">
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>16.20365524291992</v>
+        <v>16.18479537963867</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>19.95678520202637</v>
+        <v>19.93355178833008</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2316224273375818</v>
+        <v>0.2316221070924096</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>23.16224273375818</v>
+        <v>23.16221070924096</v>
       </c>
     </row>
     <row r="56">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>19.95678520202637</v>
+        <v>19.93355178833008</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>19.45443153381348</v>
+        <v>19.43178749084473</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.02517207371465235</v>
+        <v>-0.02517184608209688</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>-2.517207371465235</v>
+        <v>-2.517184608209688</v>
       </c>
     </row>
     <row r="57">
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>19.45443153381348</v>
+        <v>19.43178749084473</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>22.33777809143066</v>
+        <v>22.31176948547363</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1482102703749366</v>
+        <v>0.1482098338089488</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>14.82102703749366</v>
+        <v>14.82098338089488</v>
       </c>
     </row>
     <row r="58">
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>22.33777809143066</v>
+        <v>22.31176948547363</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -2421,13 +2421,13 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>20.67229652404785</v>
+        <v>20.64822959899902</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-0.07455896287293373</v>
+        <v>-0.07455885054556877</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>-7.455896287293373</v>
+        <v>-7.455885054556877</v>
       </c>
     </row>
     <row r="59">
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>20.67229652404785</v>
+        <v>20.64822959899902</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25.51306533813477</v>
+        <v>25.48336601257324</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2341669590727717</v>
+        <v>0.2341671178340934</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>23.41669590727717</v>
+        <v>23.41671178340934</v>
       </c>
     </row>
     <row r="60">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>25.51306533813477</v>
+        <v>25.48336601257324</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>32.60707092285156</v>
+        <v>32.56910705566406</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2780538320541703</v>
+        <v>0.2780535757950808</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>27.80538320541703</v>
+        <v>27.80535757950808</v>
       </c>
     </row>
     <row r="61">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>32.60707092285156</v>
+        <v>32.56910705566406</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>29.35254859924316</v>
+        <v>29.31838035583496</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-0.09981032430998205</v>
+        <v>-0.09981012664158295</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>-9.981032430998205</v>
+        <v>-9.981012664158296</v>
       </c>
     </row>
     <row r="62">
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>29.35254859924316</v>
+        <v>29.31838035583496</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -2557,13 +2557,13 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>24.43733787536621</v>
+        <v>24.40889167785645</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-0.1674543083459433</v>
+        <v>-0.1674542938045153</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>-16.74543083459433</v>
+        <v>-16.74542938045153</v>
       </c>
     </row>
     <row r="63">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>24.43733787536621</v>
+        <v>24.40889167785645</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>24.33654022216797</v>
+        <v>24.30820655822754</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-0.004124739515913078</v>
+        <v>-0.004124936148585889</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>-0.4124739515913078</v>
+        <v>-0.4124936148585889</v>
       </c>
     </row>
     <row r="64">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>24.33654022216797</v>
+        <v>24.30820655822754</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -2625,13 +2625,13 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>27.23641204833984</v>
+        <v>27.2047061920166</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1191571110642262</v>
+        <v>0.1191572741843718</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>11.91571110642262</v>
+        <v>11.91572741843718</v>
       </c>
     </row>
     <row r="65">
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>27.23641204833984</v>
+        <v>27.2047061920166</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -2659,13 +2659,13 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>18.51329612731934</v>
+        <v>18.49174118041992</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-0.3202740473135195</v>
+        <v>-0.3202741816102964</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>-32.02740473135195</v>
+        <v>-32.02741816102964</v>
       </c>
     </row>
     <row r="66">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>18.51329612731934</v>
+        <v>18.49174118041992</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18.63806915283203</v>
+        <v>18.61637306213379</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.006739644018796564</v>
+        <v>0.006739867300643132</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.6739644018796564</v>
+        <v>0.6739867300643132</v>
       </c>
     </row>
     <row r="67">
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>18.63806915283203</v>
+        <v>18.61637306213379</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>15.13465309143066</v>
+        <v>15.11703300476074</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.1879709766432016</v>
+        <v>-0.1879710965016489</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>-18.79709766432016</v>
+        <v>-18.79710965016489</v>
       </c>
     </row>
     <row r="68">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>15.13465309143066</v>
+        <v>15.11703300476074</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.13382720947266</v>
+        <v>18.11271858215332</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1981660299660348</v>
+        <v>0.1981662391323191</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>19.81660299660348</v>
+        <v>19.81662391323191</v>
       </c>
     </row>
     <row r="69">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>18.13382720947266</v>
+        <v>18.11271858215332</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -2795,13 +2795,13 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>15.0697546005249</v>
+        <v>15.05220985412598</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.1689699903695542</v>
+        <v>-0.168970147366111</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>-16.89699903695542</v>
+        <v>-16.8970147366111</v>
       </c>
     </row>
     <row r="70">
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>15.0697546005249</v>
+        <v>15.05220985412598</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -2829,13 +2829,13 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>12.12310409545898</v>
+        <v>12.10898780822754</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-0.1955340735915687</v>
+        <v>-0.195534215535247</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>-19.55340735915687</v>
+        <v>-19.5534215535247</v>
       </c>
     </row>
     <row r="71">
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>12.12310409545898</v>
+        <v>12.10898780822754</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -2863,13 +2863,13 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>13.47932434082031</v>
+        <v>13.46363067626953</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1118707085810915</v>
+        <v>0.1118708590260178</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>11.18707085810915</v>
+        <v>11.18708590260178</v>
       </c>
     </row>
     <row r="72">
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>13.47932434082031</v>
+        <v>13.46363067626953</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -2897,13 +2897,13 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>16.90515899658203</v>
+        <v>16.8854808807373</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2541547757988909</v>
+        <v>0.2541550854108761</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>25.41547757988909</v>
+        <v>25.4155085410876</v>
       </c>
     </row>
     <row r="73">
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>16.90515899658203</v>
+        <v>16.8854808807373</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
@@ -2931,13 +2931,13 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>14.59859466552734</v>
+        <v>14.58159923553467</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>-0.1364414455682458</v>
+        <v>-0.1364415773216663</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>-13.64414455682458</v>
+        <v>-13.64415773216663</v>
       </c>
     </row>
     <row r="74">
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>14.59859466552734</v>
+        <v>14.58159923553467</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
@@ -2965,13 +2965,13 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>19.51640510559082</v>
+        <v>19.49368858337402</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.3368687570781206</v>
+        <v>0.3368690408023851</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>33.68687570781206</v>
+        <v>33.68690408023851</v>
       </c>
     </row>
     <row r="75">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>19.51640510559082</v>
+        <v>19.49368858337402</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -2999,13 +2999,13 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>23.19152641296387</v>
+        <v>23.16452598571777</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1883093370674214</v>
+        <v>0.1883090204628883</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>18.83093370674214</v>
+        <v>18.83090204628883</v>
       </c>
     </row>
     <row r="76">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>23.19152641296387</v>
+        <v>23.16452598571777</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -3033,13 +3033,13 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>27.75243186950684</v>
+        <v>27.72012519836426</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1966625816398813</v>
+        <v>0.1966627426546637</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>19.66625816398813</v>
+        <v>19.66627426546637</v>
       </c>
     </row>
     <row r="77">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>27.75243186950684</v>
+        <v>27.72012519836426</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>27.72445487976074</v>
+        <v>27.69218635559082</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>-0.001008091466637717</v>
+        <v>-0.001007890208774564</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>-0.1008091466637717</v>
+        <v>-0.1007890208774564</v>
       </c>
     </row>
     <row r="78">
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>27.72445487976074</v>
+        <v>27.69218635559082</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -3101,13 +3101,13 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>37.80053329467773</v>
+        <v>37.75652694702148</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.3634364844544762</v>
+        <v>0.3634361137902264</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>36.34364844544762</v>
+        <v>36.34361137902265</v>
       </c>
     </row>
     <row r="79">
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>37.80053329467773</v>
+        <v>37.75652694702148</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>42.26895141601562</v>
+        <v>42.21975326538086</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.118210451860663</v>
+        <v>0.1182107222049846</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>11.8210451860663</v>
+        <v>11.82107222049846</v>
       </c>
     </row>
     <row r="80">
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>42.26895141601562</v>
+        <v>42.21975326538086</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -3169,13 +3169,13 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>46.69250106811523</v>
+        <v>46.63814544677734</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.1046524577475925</v>
+        <v>0.1046522501830784</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>10.46524577475925</v>
+        <v>10.46522501830784</v>
       </c>
     </row>
     <row r="81">
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>46.69250106811523</v>
+        <v>46.63814544677734</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
@@ -3203,13 +3203,13 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>49.31644821166992</v>
+        <v>49.25904083251953</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05619632882219916</v>
+        <v>0.05619638947121319</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>5.619632882219916</v>
+        <v>5.619638947121319</v>
       </c>
     </row>
     <row r="82">
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>49.31644821166992</v>
+        <v>49.25904083251953</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>43.46859741210938</v>
+        <v>43.41800308227539</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-0.1185781014573704</v>
+        <v>-0.1185779838893664</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>-11.85781014573704</v>
+        <v>-11.85779838893664</v>
       </c>
     </row>
     <row r="83">
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>43.46859741210938</v>
+        <v>43.41800308227539</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -3271,13 +3271,13 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>40.75150299072266</v>
+        <v>40.70405960083008</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>-0.06250706448213572</v>
+        <v>-0.06250733080244375</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>-6.250706448213572</v>
+        <v>-6.250733080244375</v>
       </c>
     </row>
     <row r="84">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>40.75150299072266</v>
+        <v>40.70405960083008</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
@@ -3305,13 +3305,13 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>46.73731994628906</v>
+        <v>46.68291473388672</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.146885796014177</v>
+        <v>0.1468859664536928</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>14.6885796014177</v>
+        <v>14.68859664536928</v>
       </c>
     </row>
     <row r="85">
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>46.73731994628906</v>
+        <v>46.68291473388672</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -3339,13 +3339,13 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>49.49174499511719</v>
+        <v>49.43412399291992</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05893416764148074</v>
+        <v>0.05893396491449421</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>5.893416764148074</v>
+        <v>5.893396491449421</v>
       </c>
     </row>
     <row r="86">
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>49.49174499511719</v>
+        <v>49.43412399291992</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -3373,13 +3373,13 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>61.48941421508789</v>
+        <v>61.41783142089844</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.2424175834001081</v>
+        <v>0.2424177159424299</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>24.24175834001081</v>
+        <v>24.24177159424299</v>
       </c>
     </row>
     <row r="87">
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>61.48941421508789</v>
+        <v>61.41783142089844</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -3407,13 +3407,13 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>79.06366729736328</v>
+        <v>78.97163391113281</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.2858094081170013</v>
+        <v>0.2858095456014653</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>28.58094081170013</v>
+        <v>28.58095456014653</v>
       </c>
     </row>
     <row r="88">
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>79.06366729736328</v>
+        <v>78.97163391113281</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
@@ -3441,13 +3441,13 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>90.30503845214844</v>
+        <v>90.19991302490234</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.1421812513768894</v>
+        <v>0.1421811675620739</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>14.21812513768894</v>
+        <v>14.21811675620739</v>
       </c>
     </row>
     <row r="89">
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>90.30503845214844</v>
+        <v>90.19991302490234</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -3475,13 +3475,13 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>86.35327911376953</v>
+        <v>86.25274658203125</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>-0.04376012021159703</v>
+        <v>-0.04376020231617472</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>-4.376012021159703</v>
+        <v>-4.376020231617472</v>
       </c>
     </row>
     <row r="90">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>86.35327911376953</v>
+        <v>86.25274658203125</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>109.571174621582</v>
+        <v>109.4436187744141</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.2688710347319083</v>
+        <v>0.2688711155456016</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>26.88710347319083</v>
+        <v>26.88711155456016</v>
       </c>
     </row>
     <row r="91">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>109.571174621582</v>
+        <v>109.4436187744141</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -3543,13 +3543,13 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>123.4804611206055</v>
+        <v>123.3367233276367</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.1269429350106077</v>
+        <v>0.1269430297426406</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>12.69429350106077</v>
+        <v>12.69430297426406</v>
       </c>
     </row>
     <row r="92">
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>123.4804611206055</v>
+        <v>123.3367233276367</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -3577,13 +3577,13 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>116.9635848999023</v>
+        <v>116.8274383544922</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-0.0527765782664027</v>
+        <v>-0.05277653562964368</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>-5.27765782664027</v>
+        <v>-5.277653562964368</v>
       </c>
     </row>
     <row r="93">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>116.9635848999023</v>
+        <v>116.8274383544922</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
@@ -3611,13 +3611,13 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>119.3124694824219</v>
+        <v>119.173583984375</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02008218698605813</v>
+        <v>0.02008214562373478</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>2.008218698605813</v>
+        <v>2.008214562373478</v>
       </c>
     </row>
     <row r="94">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>119.3124694824219</v>
+        <v>119.173583984375</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -3645,13 +3645,13 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>121.3918609619141</v>
+        <v>121.2505493164062</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.0174281153387621</v>
+        <v>0.0174280680549439</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>1.74281153387621</v>
+        <v>1.74280680549439</v>
       </c>
     </row>
     <row r="95">
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>121.3918609619141</v>
+        <v>121.2505493164062</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>132.7073822021484</v>
+        <v>132.5528564453125</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.09321482635301681</v>
+        <v>0.09321448185288306</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>9.321482635301681</v>
+        <v>9.321448185288306</v>
       </c>
     </row>
     <row r="96">
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>132.7073822021484</v>
+        <v>132.5528564453125</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -3713,13 +3713,13 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>138.1952056884766</v>
+        <v>138.0343170166016</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.04135281244542011</v>
+        <v>0.04135301734180707</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>4.135281244542011</v>
+        <v>4.135301734180707</v>
       </c>
     </row>
     <row r="97">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>138.1952056884766</v>
+        <v>138.0343170166016</v>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
@@ -3747,13 +3747,13 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>134.2460174560547</v>
+        <v>134.0897369384766</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>-0.02857688306006967</v>
+        <v>-0.02857680729967016</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>-2.857688306006967</v>
+        <v>-2.857680729967016</v>
       </c>
     </row>
     <row r="98">
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>134.2460174560547</v>
+        <v>134.0897369384766</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -3781,13 +3781,13 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>120.0306701660156</v>
+        <v>119.8909378051758</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-0.1058902719009333</v>
+        <v>-0.1058902751059577</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>-10.58902719009333</v>
+        <v>-10.58902751059577</v>
       </c>
     </row>
     <row r="99">
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>120.0306701660156</v>
+        <v>119.8909378051758</v>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
@@ -3815,13 +3815,13 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>124.8790817260742</v>
+        <v>124.7337036132812</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.0403931058066469</v>
+        <v>0.04039309306242167</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>4.03931058066469</v>
+        <v>4.039309306242167</v>
       </c>
     </row>
     <row r="100">
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>124.8790817260742</v>
+        <v>124.7337036132812</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -3849,13 +3849,13 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>108.3544616699219</v>
+        <v>108.2283248901367</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-0.1323249644996555</v>
+        <v>-0.1323249309931265</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>-13.23249644996555</v>
+        <v>-13.23249309931265</v>
       </c>
     </row>
     <row r="101">
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>108.3544616699219</v>
+        <v>108.2283248901367</v>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
@@ -3883,13 +3883,13 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>108.8943328857422</v>
+        <v>108.7675628662109</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.004982454875415376</v>
+        <v>0.004982410811787075</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0.4982454875415376</v>
+        <v>0.4982410811787075</v>
       </c>
     </row>
     <row r="102">
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>108.8943328857422</v>
+        <v>108.7675628662109</v>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
@@ -3917,13 +3917,13 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>135.0981750488281</v>
+        <v>134.9409027099609</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.2406354992833322</v>
+        <v>0.2406355273027898</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>24.06354992833322</v>
+        <v>24.06355273027898</v>
       </c>
     </row>
     <row r="103">
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>135.0981750488281</v>
+        <v>134.9409027099609</v>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
@@ -3951,13 +3951,13 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>157.9637603759766</v>
+        <v>157.7798614501953</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.1692516225247618</v>
+        <v>0.1692515633256428</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>16.92516225247618</v>
+        <v>16.92515633256428</v>
       </c>
     </row>
     <row r="104">
@@ -3977,7 +3977,7 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>157.9637603759766</v>
+        <v>157.7798614501953</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>177.8404388427734</v>
+        <v>177.6334075927734</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.1258306235524371</v>
+        <v>0.1258306729394936</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>12.58306235524371</v>
+        <v>12.58306729394936</v>
       </c>
     </row>
     <row r="105">
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>177.8404388427734</v>
+        <v>177.6334075927734</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -4019,13 +4019,13 @@
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>174.1510467529297</v>
+        <v>173.9483032226562</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>-0.02074551836382665</v>
+        <v>-0.02074555918313137</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>-2.074551836382665</v>
+        <v>-2.074555918313137</v>
       </c>
     </row>
     <row r="106">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>174.1510467529297</v>
+        <v>173.9483032226562</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
@@ -4053,13 +4053,13 @@
         </is>
       </c>
       <c r="F106" s="3" t="n">
-        <v>186.5595092773438</v>
+        <v>186.3423309326172</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.07125115097366086</v>
+        <v>0.07125121360969189</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>7.125115097366086</v>
+        <v>7.125121360969189</v>
       </c>
     </row>
     <row r="107">
@@ -4079,7 +4079,7 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>186.5595092773438</v>
+        <v>186.3423309326172</v>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
@@ -4087,13 +4087,13 @@
         </is>
       </c>
       <c r="F107" s="3" t="n">
-        <v>202.4677734375</v>
+        <v>202.2320709228516</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0.08527179462348733</v>
+        <v>0.0852717678839181</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>8.527179462348734</v>
+        <v>8.527176788391809</v>
       </c>
     </row>
     <row r="108">
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>202.4677734375</v>
+        <v>202.2320709228516</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
@@ -4121,13 +4121,13 @@
         </is>
       </c>
       <c r="F108" s="3" t="n">
-        <v>176.9805603027344</v>
+        <v>176.7745361328125</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>-0.1258828143464189</v>
+        <v>-0.125882777513319</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>-12.58828143464189</v>
+        <v>-12.5882777513319</v>
       </c>
     </row>
     <row r="109">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>176.9805603027344</v>
+        <v>176.7745361328125</v>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
@@ -4155,13 +4155,13 @@
         </is>
       </c>
       <c r="F109" s="3" t="n">
-        <v>186.4899139404297</v>
+        <v>186.2728118896484</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>0.0537310630129606</v>
+        <v>0.05373101785259271</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>5.37310630129606</v>
+        <v>5.373101785259271</v>
       </c>
     </row>
     <row r="110">
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>186.4899139404297</v>
+        <v>186.2728118896484</v>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
@@ -4189,13 +4189,13 @@
         </is>
       </c>
       <c r="F110" s="3" t="n">
-        <v>191.1196594238281</v>
+        <v>190.8971710205078</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0.02482571515839349</v>
+        <v>0.02482573320254033</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>2.482571515839349</v>
+        <v>2.482573320254033</v>
       </c>
     </row>
     <row r="111">
@@ -4215,7 +4215,7 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>191.1196594238281</v>
+        <v>190.8971710205078</v>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="F111" s="3" t="n">
-        <v>177.180419921875</v>
+        <v>176.9741516113281</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>-0.07293461878268304</v>
+        <v>-0.07293465552553402</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>-7.293461878268303</v>
+        <v>-7.293465552553402</v>
       </c>
     </row>
     <row r="112">
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>177.180419921875</v>
+        <v>176.9741516113281</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -4257,13 +4257,13 @@
         </is>
       </c>
       <c r="F112" s="3" t="n">
-        <v>174.3999938964844</v>
+        <v>174.1969757080078</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>-0.01569262578007558</v>
+        <v>-0.0156925510196515</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>-1.569262578007558</v>
+        <v>-1.56925510196515</v>
       </c>
     </row>
     <row r="113">
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>174.3999938964844</v>
+        <v>174.1969757080078</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -4291,13 +4291,13 @@
         </is>
       </c>
       <c r="F113" s="3" t="n">
-        <v>199.5700073242188</v>
+        <v>199.3376770019531</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0.1443234765402235</v>
+        <v>0.1443234085538123</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>14.43234765402235</v>
+        <v>14.43234085538123</v>
       </c>
     </row>
     <row r="114">
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>199.5700073242188</v>
+        <v>199.3376770019531</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -4325,17 +4325,51 @@
         </is>
       </c>
       <c r="F114" s="3" t="n">
-        <v>211.1399993896484</v>
+        <v>210.8942108154297</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0.05797460360179896</v>
+        <v>0.05797465881657349</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>5.797460360179896</v>
+        <v>5.797465881657349</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>210.8942108154297</v>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>200.0899963378906</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>-0.05123049341072095</v>
+      </c>
+      <c r="H115" s="3" t="n">
+        <v>-5.123049341072095</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H114"/>
+  <autoFilter ref="A1:H115"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4385,7 +4419,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to May 2026; 113 monthly observations</t>
+          <t>Jan 2017 to Jun 2026; 114 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/NVIDIA Returns - Current.xlsx
+++ b/isolated_excel/NVIDIA Returns - Current.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Returns" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Returns" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Returns'!$A$1:$H$115</definedName>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.625491857528687</v>
+        <v>2.625490665435791</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.685507774353027</v>
+        <v>2.685508012771606</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.0228589232346097</v>
+        <v>0.02285947846851455</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>2.28589232346097</v>
+        <v>2.285947846851455</v>
       </c>
     </row>
     <row r="3">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.685507774353027</v>
+        <v>2.685508012771606</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.499260902404785</v>
+        <v>2.499259471893311</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.06935257224980906</v>
+        <v>-0.06935318755056563</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-6.935257224980907</v>
+        <v>-6.935318755056564</v>
       </c>
     </row>
     <row r="4">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.499260902404785</v>
+        <v>2.499259471893311</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -588,10 +588,10 @@
         <v>2.682740211486816</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.07341342750790347</v>
+        <v>0.07341404190198397</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>7.341342750790347</v>
+        <v>7.341404190198397</v>
       </c>
     </row>
     <row r="5">
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.568711996078491</v>
+        <v>2.568711280822754</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.04250438224323216</v>
+        <v>-0.04250464885709748</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-4.250438224323217</v>
+        <v>-4.250464885709748</v>
       </c>
     </row>
     <row r="6">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.568711996078491</v>
+        <v>2.568711280822754</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -653,13 +653,13 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3.558811664581299</v>
+        <v>3.558812141418457</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3854459628071725</v>
+        <v>0.3854465342164011</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>38.54459628071724</v>
+        <v>38.54465342164011</v>
       </c>
     </row>
     <row r="7">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.558811664581299</v>
+        <v>3.558812141418457</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.563989877700806</v>
+        <v>3.563989400863647</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.001455039942417358</v>
+        <v>0.00145477177200104</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.1455039942417358</v>
+        <v>0.145477177200104</v>
       </c>
     </row>
     <row r="8">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.563989877700806</v>
+        <v>3.563989400863647</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -721,13 +721,13 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4.006530284881592</v>
+        <v>4.006529808044434</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1241699394124758</v>
+        <v>0.1241699560255558</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12.41699394124758</v>
+        <v>12.41699560255558</v>
       </c>
     </row>
     <row r="9">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4.006530284881592</v>
+        <v>4.006529808044434</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.181059837341309</v>
+        <v>4.18105936050415</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.04356127123718334</v>
+        <v>0.04356127642162821</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>4.356127123718334</v>
+        <v>4.356127642162821</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4.181059837341309</v>
+        <v>4.18105936050415</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4.411284923553467</v>
+        <v>4.411284446716309</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05506381041381037</v>
+        <v>0.055063816693671</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>5.506381041381037</v>
+        <v>5.5063816693671</v>
       </c>
     </row>
     <row r="11">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.411284923553467</v>
+        <v>4.411284446716309</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -826,10 +826,10 @@
         <v>5.103193759918213</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1568497270875411</v>
+        <v>0.1568498521370461</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>15.68497270875411</v>
+        <v>15.68498521370461</v>
       </c>
     </row>
     <row r="12">
@@ -891,13 +891,13 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4.778075695037842</v>
+        <v>4.778074264526367</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.03592274259403894</v>
+        <v>-0.03592303122981355</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-3.592274259403894</v>
+        <v>-3.592303122981355</v>
       </c>
     </row>
     <row r="14">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.778075695037842</v>
+        <v>4.778074264526367</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6.069513320922852</v>
+        <v>6.069514274597168</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2702840449401422</v>
+        <v>0.2702846248453648</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>27.02840449401423</v>
+        <v>27.02846248453648</v>
       </c>
     </row>
     <row r="15">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6.069513320922852</v>
+        <v>6.069514274597168</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5.979395389556885</v>
+        <v>5.979394435882568</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.01484763713349335</v>
+        <v>-0.01484794905117526</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>-1.484763713349335</v>
+        <v>-1.484794905117526</v>
       </c>
     </row>
     <row r="16">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.979395389556885</v>
+        <v>5.979394435882568</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
         <v>5.722182273864746</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.04301657591357244</v>
+        <v>-0.04301642328097344</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-4.301657591357245</v>
+        <v>-4.301642328097344</v>
       </c>
     </row>
     <row r="17">
@@ -1027,13 +1027,13 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.556882858276367</v>
+        <v>5.556884288787842</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02888747818176995</v>
+        <v>-0.02888722818772815</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-2.888747818176995</v>
+        <v>-2.888722818772815</v>
       </c>
     </row>
     <row r="18">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5.556882858276367</v>
+        <v>5.556884288787842</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>6.235024929046631</v>
+        <v>6.235025405883789</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1220364164704759</v>
+        <v>0.1220362134342508</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.20364164704759</v>
+        <v>12.20362134342508</v>
       </c>
     </row>
     <row r="19">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6.235024929046631</v>
+        <v>6.235025405883789</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.857002735137939</v>
+        <v>5.857003211975098</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-0.06062881836247813</v>
+        <v>-0.06062881372575712</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>-6.062881836247813</v>
+        <v>-6.062881372575712</v>
       </c>
     </row>
     <row r="20">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.857002735137939</v>
+        <v>5.857003211975098</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6.053802967071533</v>
+        <v>6.0538010597229</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.03360084344043912</v>
+        <v>0.03360043363907228</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3.360084344043912</v>
+        <v>3.360043363907228</v>
       </c>
     </row>
     <row r="21">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.053802967071533</v>
+        <v>6.0538010597229</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>6.943196773529053</v>
+        <v>6.94319486618042</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.1469148915640635</v>
+        <v>0.1469149378519929</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>14.69148915640634</v>
+        <v>14.6914937851993</v>
       </c>
     </row>
     <row r="22">
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.943196773529053</v>
+        <v>6.94319486618042</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -1197,13 +1197,13 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>6.95160436630249</v>
+        <v>6.951603889465332</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.001210910917214925</v>
+        <v>0.001211117280586649</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.1210910917214925</v>
+        <v>0.1211117280586649</v>
       </c>
     </row>
     <row r="23">
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.95160436630249</v>
+        <v>6.951603889465332</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1231,13 +1231,13 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5.215312957763672</v>
+        <v>5.215310573577881</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-0.2497684443831978</v>
+        <v>-0.2497687358911059</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>-24.97684443831978</v>
+        <v>-24.97687358911059</v>
       </c>
     </row>
     <row r="24">
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>5.215312957763672</v>
+        <v>5.215310573577881</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -1268,10 +1268,10 @@
         <v>4.046821117401123</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-0.2240501864079119</v>
+        <v>-0.2240498316814782</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>-22.40501864079118</v>
+        <v>-22.40498316814782</v>
       </c>
     </row>
     <row r="25">
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.305699586868286</v>
+        <v>3.305700063705444</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-0.1831367162106703</v>
+        <v>-0.1831365983806144</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>-18.31367162106703</v>
+        <v>-18.31365983806144</v>
       </c>
     </row>
     <row r="26">
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3.305699586868286</v>
+        <v>3.305700063705444</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
         <v>3.559508562088013</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.07677920166368679</v>
+        <v>0.07677904634156918</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>7.677920166368679</v>
+        <v>7.677904634156918</v>
       </c>
     </row>
     <row r="27">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>4.450812339782715</v>
+        <v>4.450811862945557</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1640091618973911</v>
+        <v>0.1640090371914322</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>16.40091618973911</v>
+        <v>16.40090371914322</v>
       </c>
     </row>
     <row r="29">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.450812339782715</v>
+        <v>4.450811862945557</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -1438,10 +1438,10 @@
         <v>4.486504554748535</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.008019258562485865</v>
+        <v>0.008019366556499818</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.8019258562485865</v>
+        <v>0.8019366556499818</v>
       </c>
     </row>
     <row r="30">
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.361522197723389</v>
+        <v>3.361522436141968</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.2507480697494133</v>
+        <v>-0.2507480166081368</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-25.07480697494133</v>
+        <v>-25.07480166081368</v>
       </c>
     </row>
     <row r="31">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.361522197723389</v>
+        <v>3.361522436141968</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         <v>4.075467586517334</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2123875276734657</v>
+        <v>0.2123874416839424</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>21.23875276734657</v>
+        <v>21.23874416839424</v>
       </c>
     </row>
     <row r="32">
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4.186891078948975</v>
+        <v>4.1868896484375</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.02734005118829974</v>
+        <v>0.02733970018281529</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>2.734005118829974</v>
+        <v>2.733970018281529</v>
       </c>
     </row>
     <row r="33">
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>4.186891078948975</v>
+        <v>4.1868896484375</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
         <v>4.160977840423584</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.006189136052685562</v>
+        <v>-0.006188796502813454</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>-0.6189136052685562</v>
+        <v>-0.6188796502813454</v>
       </c>
     </row>
     <row r="34">
@@ -1605,13 +1605,13 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>4.323929786682129</v>
+        <v>4.323929309844971</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.03916193560933667</v>
+        <v>0.03916182101195664</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>3.916193560933667</v>
+        <v>3.916182101195664</v>
       </c>
     </row>
     <row r="35">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>4.323929786682129</v>
+        <v>4.323929309844971</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -1639,13 +1639,13 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.993370532989502</v>
+        <v>4.993372917175293</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1548222980792326</v>
+        <v>0.1548229768248279</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>15.48222980792326</v>
+        <v>15.48229768248279</v>
       </c>
     </row>
     <row r="36">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>4.993370532989502</v>
+        <v>4.993372917175293</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.387831687927246</v>
+        <v>5.387832164764404</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.0789969725522417</v>
+        <v>0.07899655285755292</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>7.89969725522417</v>
+        <v>7.899655285755292</v>
       </c>
     </row>
     <row r="37">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.387831687927246</v>
+        <v>5.387832164764404</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -1710,10 +1710,10 @@
         <v>5.849206447601318</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.08563273435357965</v>
+        <v>0.08563263827225942</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>8.563273435357965</v>
+        <v>8.563263827225942</v>
       </c>
     </row>
     <row r="38">
@@ -1741,13 +1741,13 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>5.87729549407959</v>
+        <v>5.877295017242432</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.00480219782459379</v>
+        <v>0.004802116302910164</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.480219782459379</v>
+        <v>0.4802116302910164</v>
       </c>
     </row>
     <row r="39">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>5.87729549407959</v>
+        <v>5.877295017242432</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>6.717551231384277</v>
+        <v>6.717551708221436</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.1429663929865543</v>
+        <v>0.142966566849871</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>14.29663929865543</v>
+        <v>14.2966566849871</v>
       </c>
     </row>
     <row r="40">
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>6.717551231384277</v>
+        <v>6.717551708221436</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>6.556621551513672</v>
+        <v>6.556620121002197</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.02395659881516721</v>
+        <v>-0.02395688104972504</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>-2.395659881516721</v>
+        <v>-2.395688104972504</v>
       </c>
     </row>
     <row r="41">
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6.556621551513672</v>
+        <v>6.556620121002197</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         <v>7.269989013671875</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1088010733200719</v>
+        <v>0.1088013152362772</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>10.88010733200719</v>
+        <v>10.88013152362772</v>
       </c>
     </row>
     <row r="42">
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>8.830546379089355</v>
+        <v>8.830545425415039</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2146574585577379</v>
+        <v>0.2146573273781289</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>21.46574585577379</v>
+        <v>21.46573273781289</v>
       </c>
     </row>
     <row r="43">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>8.830546379089355</v>
+        <v>8.830545425415039</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>9.45395565032959</v>
+        <v>9.453956604003906</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.07059690810485542</v>
+        <v>0.07059713172355564</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>7.059690810485542</v>
+        <v>7.059713172355564</v>
       </c>
     </row>
     <row r="44">
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9.45395565032959</v>
+        <v>9.453956604003906</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -1945,13 +1945,13 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.5658016204834</v>
+        <v>10.56580352783203</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1176064296551937</v>
+        <v>0.1176065186672466</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>11.76064296551937</v>
+        <v>11.76065186672466</v>
       </c>
     </row>
     <row r="45">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10.5658016204834</v>
+        <v>10.56580352783203</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -1979,13 +1979,13 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13.31282997131348</v>
+        <v>13.31282901763916</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2599924217301743</v>
+        <v>0.2599921040147133</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>25.99924217301744</v>
+        <v>25.99921040147133</v>
       </c>
     </row>
     <row r="46">
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>13.31282997131348</v>
+        <v>13.31282901763916</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>13.47214126586914</v>
+        <v>13.47213935852051</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.01196674898567385</v>
+        <v>0.01196667820718389</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>1.196674898567385</v>
+        <v>1.196667820718389</v>
       </c>
     </row>
     <row r="47">
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>13.47214126586914</v>
+        <v>13.47213935852051</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -2047,13 +2047,13 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>12.47993946075439</v>
+        <v>12.47993755340576</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>-0.07364841160242508</v>
+        <v>-0.07364842202936572</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>-7.364841160242507</v>
+        <v>-7.364842202936572</v>
       </c>
     </row>
     <row r="48">
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>12.47993946075439</v>
+        <v>12.47993755340576</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -2084,10 +2084,10 @@
         <v>13.34369659423828</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06921164451158912</v>
+        <v>0.0692118079226125</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>6.921164451158912</v>
+        <v>6.92118079226125</v>
       </c>
     </row>
     <row r="49">
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>12.93754100799561</v>
+        <v>12.93754386901855</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-0.004998333962024648</v>
+        <v>-0.004998113926192538</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>-0.4998333962024648</v>
+        <v>-0.4998113926192538</v>
       </c>
     </row>
     <row r="51">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>12.93754100799561</v>
+        <v>12.93754386901855</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>13.65938282012939</v>
+        <v>13.65937805175781</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.05579435935218902</v>
+        <v>0.05579375730410696</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>5.579435935218902</v>
+        <v>5.579375730410696</v>
       </c>
     </row>
     <row r="52">
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>13.65938282012939</v>
+        <v>13.65937805175781</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>13.29919052124023</v>
+        <v>13.29919242858887</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-0.02636958811626222</v>
+        <v>-0.02636910859368102</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>-2.636958811626222</v>
+        <v>-2.636910859368102</v>
       </c>
     </row>
     <row r="53">
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>13.29919052124023</v>
+        <v>13.29919242858887</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -2251,13 +2251,13 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14.95433521270752</v>
+        <v>14.95433712005615</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1244545439682092</v>
+        <v>0.1244545261191403</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>12.44545439682092</v>
+        <v>12.44545261191403</v>
       </c>
     </row>
     <row r="54">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>14.95433521270752</v>
+        <v>14.95433712005615</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>16.18479537963867</v>
+        <v>16.1847972869873</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.08228116793085949</v>
+        <v>0.08228115743632047</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>8.228116793085949</v>
+        <v>8.228115743632047</v>
       </c>
     </row>
     <row r="55">
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>16.18479537963867</v>
+        <v>16.1847972869873</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>19.93355178833008</v>
+        <v>19.93354988098145</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2316221070924096</v>
+        <v>0.2316218440998432</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>23.16221070924096</v>
+        <v>23.16218440998432</v>
       </c>
     </row>
     <row r="56">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>19.93355178833008</v>
+        <v>19.93354988098145</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -2356,10 +2356,10 @@
         <v>19.43178749084473</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.02517184608209688</v>
+        <v>-0.02517175280532691</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>-2.517184608209688</v>
+        <v>-2.517175280532691</v>
       </c>
     </row>
     <row r="57">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>22.31176948547363</v>
+        <v>22.31177520751953</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1482098338089488</v>
+        <v>0.148210128277273</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>14.82098338089488</v>
+        <v>14.8210128277273</v>
       </c>
     </row>
     <row r="58">
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>22.31176948547363</v>
+        <v>22.31177520751953</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -2421,13 +2421,13 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>20.64822959899902</v>
+        <v>20.64823532104492</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-0.07455885054556877</v>
+        <v>-0.07455883142431274</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>-7.455885054556877</v>
+        <v>-7.455883142431274</v>
       </c>
     </row>
     <row r="59">
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>20.64822959899902</v>
+        <v>20.64823532104492</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25.48336601257324</v>
+        <v>25.48336029052734</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2341671178340934</v>
+        <v>0.2341664987009522</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>23.41671178340934</v>
+        <v>23.41664987009522</v>
       </c>
     </row>
     <row r="60">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>25.48336601257324</v>
+        <v>25.48336029052734</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>32.56910705566406</v>
+        <v>32.5691032409668</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2780535757950808</v>
+        <v>0.2780537130761895</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>27.80535757950808</v>
+        <v>27.80537130761896</v>
       </c>
     </row>
     <row r="61">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>32.56910705566406</v>
+        <v>32.5691032409668</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>29.31838035583496</v>
+        <v>29.31838226318359</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-0.09981012664158295</v>
+        <v>-0.09980996264257924</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>-9.981012664158296</v>
+        <v>-9.980996264257925</v>
       </c>
     </row>
     <row r="62">
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>29.31838035583496</v>
+        <v>29.31838226318359</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -2557,13 +2557,13 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>24.40889167785645</v>
+        <v>24.40888977050781</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-0.1674542938045153</v>
+        <v>-0.1674544130233561</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>-16.74542938045153</v>
+        <v>-16.74544130233561</v>
       </c>
     </row>
     <row r="63">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>24.40889167785645</v>
+        <v>24.40888977050781</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>24.30820655822754</v>
+        <v>24.30820465087891</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-0.004124936148585889</v>
+        <v>-0.00412493647091472</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>-0.4124936148585889</v>
+        <v>-0.412493647091472</v>
       </c>
     </row>
     <row r="64">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>24.30820655822754</v>
+        <v>24.30820465087891</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -2625,13 +2625,13 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>27.2047061920166</v>
+        <v>27.20470428466797</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1191572741843718</v>
+        <v>0.1191572835340735</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>11.91572741843718</v>
+        <v>11.91572835340735</v>
       </c>
     </row>
     <row r="65">
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>27.2047061920166</v>
+        <v>27.20470428466797</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -2662,10 +2662,10 @@
         <v>18.49174118041992</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-0.3202741816102964</v>
+        <v>-0.3202741339540492</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>-32.02741816102964</v>
+        <v>-32.02741339540493</v>
       </c>
     </row>
     <row r="66">
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18.61637306213379</v>
+        <v>18.61637115478516</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.006739867300643132</v>
+        <v>0.006739764154670258</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.6739867300643132</v>
+        <v>0.6739764154670258</v>
       </c>
     </row>
     <row r="67">
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>18.61637306213379</v>
+        <v>18.61637115478516</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>15.11703300476074</v>
+        <v>15.11703109741211</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.1879710965016489</v>
+        <v>-0.1879711157603117</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>-18.79710965016489</v>
+        <v>-18.79711157603117</v>
       </c>
     </row>
     <row r="68">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>15.11703300476074</v>
+        <v>15.11703109741211</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.11271858215332</v>
+        <v>18.11271476745605</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1981662391323191</v>
+        <v>0.1981661379632127</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>19.81662391323191</v>
+        <v>19.81661379632127</v>
       </c>
     </row>
     <row r="69">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>18.11271858215332</v>
+        <v>18.11271476745605</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -2795,13 +2795,13 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>15.05220985412598</v>
+        <v>15.05221176147461</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.168970147366111</v>
+        <v>-0.1689698670395005</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>-16.8970147366111</v>
+        <v>-16.89698670395004</v>
       </c>
     </row>
     <row r="70">
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>15.05220985412598</v>
+        <v>15.05221176147461</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -2829,13 +2829,13 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>12.10898780822754</v>
+        <v>12.10898971557617</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-0.195534215535247</v>
+        <v>-0.1955341907580299</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>-19.5534215535247</v>
+        <v>-19.55341907580299</v>
       </c>
     </row>
     <row r="71">
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>12.10898780822754</v>
+        <v>12.10898971557617</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -2863,13 +2863,13 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>13.46363067626953</v>
+        <v>13.46363162994385</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1118708590260178</v>
+        <v>0.1118707626471229</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>11.18708590260178</v>
+        <v>11.18707626471229</v>
       </c>
     </row>
     <row r="72">
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>13.46363067626953</v>
+        <v>13.46363162994385</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
         <v>16.8854808807373</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2541550854108761</v>
+        <v>0.2541549965748526</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>25.4155085410876</v>
+        <v>25.41549965748526</v>
       </c>
     </row>
     <row r="73">
@@ -2965,13 +2965,13 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>19.49368858337402</v>
+        <v>19.49368667602539</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.3368690408023851</v>
+        <v>0.3368689099972106</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>33.68690408023851</v>
+        <v>33.68689099972107</v>
       </c>
     </row>
     <row r="75">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>19.49368858337402</v>
+        <v>19.49368667602539</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -2999,13 +2999,13 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>23.16452598571777</v>
+        <v>23.16452980041504</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1883090204628883</v>
+        <v>0.1883093324211624</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>18.83090204628883</v>
+        <v>18.83093324211625</v>
       </c>
     </row>
     <row r="76">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>23.16452598571777</v>
+        <v>23.16452980041504</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -3033,13 +3033,13 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>27.72012519836426</v>
+        <v>27.72012710571289</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1966627426546637</v>
+        <v>0.1966626279293711</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>19.66627426546637</v>
+        <v>19.6662627929371</v>
       </c>
     </row>
     <row r="77">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>27.72012519836426</v>
+        <v>27.72012710571289</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>27.69218635559082</v>
+        <v>27.69218254089355</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>-0.001007890208774564</v>
+        <v>-0.001008096561490035</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>-0.1007890208774564</v>
+        <v>-0.1008096561490035</v>
       </c>
     </row>
     <row r="78">
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>27.69218635559082</v>
+        <v>27.69218254089355</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -3101,13 +3101,13 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>37.75652694702148</v>
+        <v>37.75653076171875</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.3634361137902264</v>
+        <v>0.3634364393620109</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>36.34361137902265</v>
+        <v>36.34364393620109</v>
       </c>
     </row>
     <row r="79">
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>37.75652694702148</v>
+        <v>37.75653076171875</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>42.21975326538086</v>
+        <v>42.21974945068359</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.1182107222049846</v>
+        <v>0.1182105081934617</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>11.82107222049846</v>
+        <v>11.82105081934617</v>
       </c>
     </row>
     <row r="80">
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>42.21975326538086</v>
+        <v>42.21974945068359</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -3169,13 +3169,13 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>46.63814544677734</v>
+        <v>46.63813781738281</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.1046522501830784</v>
+        <v>0.1046521692853788</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>10.46522501830784</v>
+        <v>10.46521692853788</v>
       </c>
     </row>
     <row r="81">
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>46.63814544677734</v>
+        <v>46.63813781738281</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
@@ -3206,10 +3206,10 @@
         <v>49.25904083251953</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05619638947121319</v>
+        <v>0.05619656225124547</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>5.619638947121319</v>
+        <v>5.619656225124547</v>
       </c>
     </row>
     <row r="82">
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>43.41800308227539</v>
+        <v>43.41799926757812</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-0.1185779838893664</v>
+        <v>-0.1185780613309324</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>-11.85779838893664</v>
+        <v>-11.85780613309324</v>
       </c>
     </row>
     <row r="83">
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>43.41800308227539</v>
+        <v>43.41799926757812</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -3274,10 +3274,10 @@
         <v>40.70405960083008</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>-0.06250733080244375</v>
+        <v>-0.06250724843451383</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>-6.250733080244375</v>
+        <v>-6.250724843451383</v>
       </c>
     </row>
     <row r="84">
@@ -3305,13 +3305,13 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>46.68291473388672</v>
+        <v>46.68291091918945</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.1468859664536928</v>
+        <v>0.1468858727358351</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>14.68859664536928</v>
+        <v>14.68858727358351</v>
       </c>
     </row>
     <row r="85">
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>46.68291473388672</v>
+        <v>46.68291091918945</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -3339,13 +3339,13 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>49.43412399291992</v>
+        <v>49.43413543701172</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05893396491449421</v>
+        <v>0.05893429659056126</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>5.893396491449421</v>
+        <v>5.893429659056126</v>
       </c>
     </row>
     <row r="86">
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>49.43412399291992</v>
+        <v>49.43413543701172</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -3376,10 +3376,10 @@
         <v>61.41783142089844</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.2424177159424299</v>
+        <v>0.2424174283204805</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>24.24177159424299</v>
+        <v>24.24174283204805</v>
       </c>
     </row>
     <row r="87">
@@ -3441,13 +3441,13 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>90.19991302490234</v>
+        <v>90.19990539550781</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.1421811675620739</v>
+        <v>0.1421810709527707</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>14.21811675620739</v>
+        <v>14.21810709527707</v>
       </c>
     </row>
     <row r="89">
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>90.19991302490234</v>
+        <v>90.19990539550781</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -3478,10 +3478,10 @@
         <v>86.25274658203125</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>-0.04376020231617472</v>
+        <v>-0.04376012143437502</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>-4.376020231617472</v>
+        <v>-4.376012143437502</v>
       </c>
     </row>
     <row r="90">
@@ -3543,13 +3543,13 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>123.3367233276367</v>
+        <v>123.3367080688477</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.1269430297426406</v>
+        <v>0.1269428903211811</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>12.69430297426406</v>
+        <v>12.69428903211811</v>
       </c>
     </row>
     <row r="92">
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>123.3367233276367</v>
+        <v>123.3367080688477</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -3580,10 +3580,10 @@
         <v>116.8274383544922</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-0.05277653562964368</v>
+        <v>-0.05277641844244729</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>-5.277653562964368</v>
+        <v>-5.277641844244729</v>
       </c>
     </row>
     <row r="93">
@@ -3611,13 +3611,13 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>119.173583984375</v>
+        <v>119.1735763549805</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02008214562373478</v>
+        <v>0.02008208031891745</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>2.008214562373478</v>
+        <v>2.008208031891745</v>
       </c>
     </row>
     <row r="94">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>119.173583984375</v>
+        <v>119.1735763549805</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -3645,13 +3645,13 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>121.2505493164062</v>
+        <v>121.2505340576172</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.0174280680549439</v>
+        <v>0.01742800515149523</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>1.74280680549439</v>
+        <v>1.742800515149523</v>
       </c>
     </row>
     <row r="95">
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>121.2505493164062</v>
+        <v>121.2505340576172</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>132.5528564453125</v>
+        <v>132.5528869628906</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.09321448185288306</v>
+        <v>0.09321487111885762</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>9.321448185288306</v>
+        <v>9.321487111885762</v>
       </c>
     </row>
     <row r="96">
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>132.5528564453125</v>
+        <v>132.5528869628906</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -3716,10 +3716,10 @@
         <v>138.0343170166016</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.04135301734180707</v>
+        <v>0.04135277759167555</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>4.135301734180707</v>
+        <v>4.135277759167555</v>
       </c>
     </row>
     <row r="97">
@@ -3781,13 +3781,13 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>119.8909378051758</v>
+        <v>119.8909454345703</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-0.1058902751059577</v>
+        <v>-0.1058902182082808</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>-10.58902751059577</v>
+        <v>-10.58902182082808</v>
       </c>
     </row>
     <row r="99">
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>119.8909378051758</v>
+        <v>119.8909454345703</v>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
@@ -3815,13 +3815,13 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>124.7337036132812</v>
+        <v>124.7337112426758</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.04039309306242167</v>
+        <v>0.04039309049196182</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>4.039309306242167</v>
+        <v>4.039309049196182</v>
       </c>
     </row>
     <row r="100">
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>124.7337036132812</v>
+        <v>124.7337112426758</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -3852,10 +3852,10 @@
         <v>108.2283248901367</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-0.1323249309931265</v>
+        <v>-0.1323249840648691</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>-13.23249309931265</v>
+        <v>-13.23249840648691</v>
       </c>
     </row>
     <row r="101">
@@ -4019,13 +4019,13 @@
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>173.9483032226562</v>
+        <v>173.9483184814453</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>-0.02074555918313137</v>
+        <v>-0.02074547328268472</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>-2.074555918313137</v>
+        <v>-2.074547328268472</v>
       </c>
     </row>
     <row r="106">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>173.9483032226562</v>
+        <v>173.9483184814453</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
@@ -4056,10 +4056,10 @@
         <v>186.3423309326172</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.07125121360969189</v>
+        <v>0.07125111963927333</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>7.125121360969189</v>
+        <v>7.125111963927333</v>
       </c>
     </row>
     <row r="107">
@@ -4155,13 +4155,13 @@
         </is>
       </c>
       <c r="F109" s="3" t="n">
-        <v>186.2728118896484</v>
+        <v>186.2727966308594</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>0.05373101785259271</v>
+        <v>0.05373093153479269</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>5.373101785259271</v>
+        <v>5.373093153479269</v>
       </c>
     </row>
     <row r="110">
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>186.2728118896484</v>
+        <v>186.2727966308594</v>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
@@ -4192,10 +4192,10 @@
         <v>190.8971710205078</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0.02482573320254033</v>
+        <v>0.02482581715253174</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>2.482573320254033</v>
+        <v>2.482581715253174</v>
       </c>
     </row>
     <row r="111">

--- a/isolated_excel/NVIDIA Returns - Current.xlsx
+++ b/isolated_excel/NVIDIA Returns - Current.xlsx
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.685508012771606</v>
+        <v>2.685507774353027</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.02285947846851455</v>
+        <v>0.02285938765936324</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>2.285947846851455</v>
+        <v>2.285938765936324</v>
       </c>
     </row>
     <row r="3">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.685508012771606</v>
+        <v>2.685507774353027</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.499259471893311</v>
+        <v>2.49925971031189</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.06935318755056563</v>
+        <v>-0.06935301614831746</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-6.935318755056564</v>
+        <v>-6.935301614831745</v>
       </c>
     </row>
     <row r="4">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.499259471893311</v>
+        <v>2.49925971031189</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.682740211486816</v>
+        <v>2.682739973068237</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.07341404190198397</v>
+        <v>0.07341384410724183</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>7.341404190198397</v>
+        <v>7.341384410724183</v>
       </c>
     </row>
     <row r="5">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.682740211486816</v>
+        <v>2.682739973068237</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.568711280822754</v>
+        <v>2.56871223449707</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.04250464885709748</v>
+        <v>-0.04250420827805912</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-4.250464885709748</v>
+        <v>-4.250420827805912</v>
       </c>
     </row>
     <row r="6">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.568711280822754</v>
+        <v>2.56871223449707</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -656,10 +656,10 @@
         <v>3.558812141418457</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3854465342164011</v>
+        <v>0.3854460198478553</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>38.54465342164011</v>
+        <v>38.54460198478553</v>
       </c>
     </row>
     <row r="7">
@@ -721,13 +721,13 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4.006529808044434</v>
+        <v>4.006528377532959</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1241699560255558</v>
+        <v>0.1241695546462829</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12.41699560255558</v>
+        <v>12.41695546462829</v>
       </c>
     </row>
     <row r="9">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4.006529808044434</v>
+        <v>4.006528377532959</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.18105936050415</v>
+        <v>4.181059837341309</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.04356127642162821</v>
+        <v>0.04356176803515321</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>4.356127642162821</v>
+        <v>4.356176803515321</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4.18105936050415</v>
+        <v>4.181059837341309</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4.411284446716309</v>
+        <v>4.411284923553467</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.055063816693671</v>
+        <v>0.05506381041381037</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>5.5063816693671</v>
+        <v>5.506381041381037</v>
       </c>
     </row>
     <row r="11">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.411284446716309</v>
+        <v>4.411284923553467</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -823,13 +823,13 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5.103193759918213</v>
+        <v>5.103194236755371</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1568498521370461</v>
+        <v>0.1568498351823857</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>15.68498521370461</v>
+        <v>15.68498351823857</v>
       </c>
     </row>
     <row r="12">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>5.103193759918213</v>
+        <v>5.103194236755371</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4.956112861633301</v>
+        <v>4.956110000610352</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-0.02882134310480688</v>
+        <v>-0.02882199448448508</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>-2.882134310480688</v>
+        <v>-2.882199448448508</v>
       </c>
     </row>
     <row r="13">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4.956112861633301</v>
+        <v>4.956110000610352</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -891,13 +891,13 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4.778074264526367</v>
+        <v>4.778075695037842</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.03592303122981355</v>
+        <v>-0.03592218605934583</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-3.592303122981355</v>
+        <v>-3.592218605934583</v>
       </c>
     </row>
     <row r="14">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.778074264526367</v>
+        <v>4.778075695037842</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6.069514274597168</v>
+        <v>6.069513320922852</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2702846248453648</v>
+        <v>0.2702840449401422</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>27.02846248453648</v>
+        <v>27.02840449401423</v>
       </c>
     </row>
     <row r="15">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6.069514274597168</v>
+        <v>6.069513320922852</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5.979394435882568</v>
+        <v>5.979395389556885</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.01484794905117526</v>
+        <v>-0.01484763713349335</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>-1.484794905117526</v>
+        <v>-1.484763713349335</v>
       </c>
     </row>
     <row r="16">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.979394435882568</v>
+        <v>5.979395389556885</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5.722182273864746</v>
+        <v>5.722182750701904</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.04301642328097344</v>
+        <v>-0.04301649616685432</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-4.301642328097344</v>
+        <v>-4.301649616685433</v>
       </c>
     </row>
     <row r="17">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5.722182273864746</v>
+        <v>5.722182750701904</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -1027,13 +1027,13 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.556884288787842</v>
+        <v>5.556884765625</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02888722818772815</v>
+        <v>-0.02888722578051672</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-2.888722818772815</v>
+        <v>-2.888722578051672</v>
       </c>
     </row>
     <row r="18">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5.556884288787842</v>
+        <v>5.556884765625</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>6.235025405883789</v>
+        <v>6.235026836395264</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1220362134342508</v>
+        <v>0.1220363745826194</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.20362134342508</v>
+        <v>12.20363745826194</v>
       </c>
     </row>
     <row r="19">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6.235025405883789</v>
+        <v>6.235026836395264</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.857003211975098</v>
+        <v>5.857002258300781</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-0.06062881372575712</v>
+        <v>-0.06062918220140889</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>-6.062881372575712</v>
+        <v>-6.062918220140889</v>
       </c>
     </row>
     <row r="20">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.857003211975098</v>
+        <v>5.857002258300781</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6.0538010597229</v>
+        <v>6.053802013397217</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.03360043363907228</v>
+        <v>0.03360076476281404</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3.360043363907228</v>
+        <v>3.360076476281404</v>
       </c>
     </row>
     <row r="21">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.0538010597229</v>
+        <v>6.053802013397217</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -1166,10 +1166,10 @@
         <v>6.94319486618042</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.1469149378519929</v>
+        <v>0.146914757174905</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>14.6914937851993</v>
+        <v>14.6914757174905</v>
       </c>
     </row>
     <row r="22">
@@ -1197,13 +1197,13 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>6.951603889465332</v>
+        <v>6.951605796813965</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.001211117280586649</v>
+        <v>0.001211391988220623</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.1211117280586649</v>
+        <v>0.1211391988220623</v>
       </c>
     </row>
     <row r="23">
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.951603889465332</v>
+        <v>6.951605796813965</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1234,10 +1234,10 @@
         <v>5.215310573577881</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-0.2497687358911059</v>
+        <v>-0.2497689417360024</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>-24.97687358911059</v>
+        <v>-24.97689417360024</v>
       </c>
     </row>
     <row r="24">
@@ -1333,13 +1333,13 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3.559508562088013</v>
+        <v>3.559508323669434</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.07677904634156918</v>
+        <v>0.0767789742180931</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>7.677904634156918</v>
+        <v>7.67789742180931</v>
       </c>
     </row>
     <row r="27">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.559508562088013</v>
+        <v>3.559508323669434</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -1367,13 +1367,13 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.823691844940186</v>
+        <v>3.823692321777344</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.07421903283671338</v>
+        <v>0.07421923875024605</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>7.421903283671338</v>
+        <v>7.421923875024605</v>
       </c>
     </row>
     <row r="28">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.823691844940186</v>
+        <v>3.823692321777344</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>4.450811862945557</v>
+        <v>4.450810432434082</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1640090371914322</v>
+        <v>0.164008517914757</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>16.40090371914322</v>
+        <v>16.4008517914757</v>
       </c>
     </row>
     <row r="29">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.450811862945557</v>
+        <v>4.450810432434082</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -1438,10 +1438,10 @@
         <v>4.486504554748535</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.008019366556499818</v>
+        <v>0.008019690538680679</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.8019366556499818</v>
+        <v>0.8019690538680679</v>
       </c>
     </row>
     <row r="30">
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.361522436141968</v>
+        <v>3.361522197723389</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.2507480166081368</v>
+        <v>-0.2507480697494133</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-25.07480166081368</v>
+        <v>-25.07480697494133</v>
       </c>
     </row>
     <row r="31">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.361522436141968</v>
+        <v>3.361522197723389</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.075467586517334</v>
+        <v>4.075469017028809</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2123874416839424</v>
+        <v>0.2123879532281372</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>21.23874416839424</v>
+        <v>21.23879532281372</v>
       </c>
     </row>
     <row r="32">
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>4.075467586517334</v>
+        <v>4.075469017028809</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4.1868896484375</v>
+        <v>4.186890125274658</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.02733970018281529</v>
+        <v>0.02733945658285974</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>2.733970018281529</v>
+        <v>2.733945658285974</v>
       </c>
     </row>
     <row r="33">
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>4.1868896484375</v>
+        <v>4.186890125274658</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4.160977840423584</v>
+        <v>4.1609787940979</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.006188796502813454</v>
+        <v>-0.006188681909835902</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>-0.6188796502813454</v>
+        <v>-0.6188681909835902</v>
       </c>
     </row>
     <row r="34">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>4.160977840423584</v>
+        <v>4.1609787940979</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -1605,13 +1605,13 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>4.323929309844971</v>
+        <v>4.323929786682129</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.03916182101195664</v>
+        <v>0.03916169743892106</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>3.916182101195664</v>
+        <v>3.916169743892106</v>
       </c>
     </row>
     <row r="35">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>4.323929309844971</v>
+        <v>4.323929786682129</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -1639,13 +1639,13 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.993372917175293</v>
+        <v>4.993371963500977</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1548229768248279</v>
+        <v>0.1548226289151955</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>15.48229768248279</v>
+        <v>15.48226289151955</v>
       </c>
     </row>
     <row r="36">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>4.993372917175293</v>
+        <v>4.993371963500977</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.387832164764404</v>
+        <v>5.387831687927246</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.07899655285755292</v>
+        <v>0.07899666343896872</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>7.899655285755292</v>
+        <v>7.899666343896872</v>
       </c>
     </row>
     <row r="37">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.387832164764404</v>
+        <v>5.387831687927246</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -1707,13 +1707,13 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.849206447601318</v>
+        <v>5.849205493927002</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.08563263827225942</v>
+        <v>0.08563255734836273</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>8.563263827225942</v>
+        <v>8.563255734836272</v>
       </c>
     </row>
     <row r="38">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>5.849206447601318</v>
+        <v>5.849205493927002</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -1741,13 +1741,13 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>5.877295017242432</v>
+        <v>5.877296924591064</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.004802116302910164</v>
+        <v>0.004802606216045779</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.4802116302910164</v>
+        <v>0.4802606216045779</v>
       </c>
     </row>
     <row r="39">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>5.877295017242432</v>
+        <v>5.877296924591064</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>6.717551708221436</v>
+        <v>6.717551231384277</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.142966566849871</v>
+        <v>0.1429661147929286</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>14.2966566849871</v>
+        <v>14.29661147929286</v>
       </c>
     </row>
     <row r="40">
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>6.717551708221436</v>
+        <v>6.717551231384277</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>6.556620121002197</v>
+        <v>6.556621074676514</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.02395688104972504</v>
+        <v>-0.02395666979894417</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>-2.395688104972504</v>
+        <v>-2.395666979894417</v>
       </c>
     </row>
     <row r="41">
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6.556620121002197</v>
+        <v>6.556621074676514</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -1843,13 +1843,13 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>7.269989013671875</v>
+        <v>7.269989967346191</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1088013152362772</v>
+        <v>0.1088012994108971</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>10.88013152362772</v>
+        <v>10.88012994108971</v>
       </c>
     </row>
     <row r="42">
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>7.269989013671875</v>
+        <v>7.269989967346191</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>8.830545425415039</v>
+        <v>8.830544471740723</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2146573273781289</v>
+        <v>0.2146570368602847</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>21.46573273781289</v>
+        <v>21.46570368602847</v>
       </c>
     </row>
     <row r="43">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>8.830545425415039</v>
+        <v>8.830544471740723</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>9.453956604003906</v>
+        <v>9.45395565032959</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.07059713172355564</v>
+        <v>0.07059713934785017</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>7.059713172355564</v>
+        <v>7.059713934785017</v>
       </c>
     </row>
     <row r="44">
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9.453956604003906</v>
+        <v>9.45395565032959</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -1945,13 +1945,13 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.56580352783203</v>
+        <v>10.56580543518066</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1176065186672466</v>
+        <v>0.1176068331579609</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>11.76065186672466</v>
+        <v>11.76068331579609</v>
       </c>
     </row>
     <row r="45">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10.56580352783203</v>
+        <v>10.56580543518066</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -1979,13 +1979,13 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13.31282901763916</v>
+        <v>13.31282997131348</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2599921040147133</v>
+        <v>0.2599919668202599</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>25.99921040147133</v>
+        <v>25.99919668202599</v>
       </c>
     </row>
     <row r="46">
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>13.31282901763916</v>
+        <v>13.31282997131348</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>13.47213935852051</v>
+        <v>13.47213745117188</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.01196667820718389</v>
+        <v>0.01196646244274691</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>1.196667820718389</v>
+        <v>1.196646244274691</v>
       </c>
     </row>
     <row r="47">
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>13.47213935852051</v>
+        <v>13.47213745117188</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -2050,10 +2050,10 @@
         <v>12.47993755340576</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>-0.07364842202936572</v>
+        <v>-0.07364829087902502</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>-7.364842202936572</v>
+        <v>-7.364829087902502</v>
       </c>
     </row>
     <row r="48">
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>13.00253200531006</v>
+        <v>13.00253105163574</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>-0.02556747199089759</v>
+        <v>-0.0255675434609216</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>-2.556747199089759</v>
+        <v>-2.55675434609216</v>
       </c>
     </row>
     <row r="50">
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>13.00253200531006</v>
+        <v>13.00253105163574</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>12.93754386901855</v>
+        <v>12.93754291534424</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-0.004998113926192538</v>
+        <v>-0.004998114292780631</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>-0.4998113926192538</v>
+        <v>-0.4998114292780631</v>
       </c>
     </row>
     <row r="51">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>12.93754386901855</v>
+        <v>12.93754291534424</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>13.65937805175781</v>
+        <v>13.65937995910645</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.05579375730410696</v>
+        <v>0.05579398255800871</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>5.579375730410696</v>
+        <v>5.579398255800871</v>
       </c>
     </row>
     <row r="52">
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>13.65937805175781</v>
+        <v>13.65937995910645</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>13.29919242858887</v>
+        <v>13.29919147491455</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-0.02636910859368102</v>
+        <v>-0.02636931436640821</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>-2.636910859368102</v>
+        <v>-2.636931436640821</v>
       </c>
     </row>
     <row r="53">
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>13.29919242858887</v>
+        <v>13.29919147491455</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -2251,13 +2251,13 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14.95433712005615</v>
+        <v>14.95433521270752</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1244545261191403</v>
+        <v>0.1244544633344791</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>12.44545261191403</v>
+        <v>12.44544633344791</v>
       </c>
     </row>
     <row r="54">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>14.95433712005615</v>
+        <v>14.95433521270752</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>16.1847972869873</v>
+        <v>16.18479537963867</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.08228115743632047</v>
+        <v>0.08228116793085949</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>8.228115743632047</v>
+        <v>8.228116793085949</v>
       </c>
     </row>
     <row r="55">
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>16.1847972869873</v>
+        <v>16.18479537963867</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>19.93354988098145</v>
+        <v>19.93355369567871</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2316218440998432</v>
+        <v>0.2316222249405868</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>23.16218440998432</v>
+        <v>23.16222249405868</v>
       </c>
     </row>
     <row r="56">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>19.93354988098145</v>
+        <v>19.93355369567871</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>19.43178749084473</v>
+        <v>19.43178939819336</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.02517175280532691</v>
+        <v>-0.02517184367352054</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>-2.517175280532691</v>
+        <v>-2.517184367352054</v>
       </c>
     </row>
     <row r="57">
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>19.43178749084473</v>
+        <v>19.43178939819336</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>22.31177520751953</v>
+        <v>22.31177711486816</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.148210128277273</v>
+        <v>0.1482101137295451</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>14.8210128277273</v>
+        <v>14.82101137295451</v>
       </c>
     </row>
     <row r="58">
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>22.31177520751953</v>
+        <v>22.31177711486816</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -2421,13 +2421,13 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>20.64823532104492</v>
+        <v>20.64823150634766</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-0.07455883142431274</v>
+        <v>-0.07455908150910806</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>-7.455883142431274</v>
+        <v>-7.455908150910806</v>
       </c>
     </row>
     <row r="59">
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>20.64823532104492</v>
+        <v>20.64823150634766</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25.48336029052734</v>
+        <v>25.48336410522461</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2341664987009522</v>
+        <v>0.2341669114563416</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>23.41664987009522</v>
+        <v>23.41669114563416</v>
       </c>
     </row>
     <row r="60">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>25.48336029052734</v>
+        <v>25.48336410522461</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -2492,10 +2492,10 @@
         <v>32.5691032409668</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2780537130761895</v>
+        <v>0.2780535217596904</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>27.80537130761896</v>
+        <v>27.80535217596904</v>
       </c>
     </row>
     <row r="61">
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>29.31838226318359</v>
+        <v>29.31838035583496</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-0.09980996264257924</v>
+        <v>-0.09981002120570948</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>-9.980996264257925</v>
+        <v>-9.981002120570947</v>
       </c>
     </row>
     <row r="62">
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>29.31838226318359</v>
+        <v>29.31838035583496</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -2557,13 +2557,13 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>24.40888977050781</v>
+        <v>24.40889358520508</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-0.1674544130233561</v>
+        <v>-0.1674542287481032</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>-16.74544130233561</v>
+        <v>-16.74542287481032</v>
       </c>
     </row>
     <row r="63">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>24.40888977050781</v>
+        <v>24.40889358520508</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>24.30820465087891</v>
+        <v>24.30820846557617</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-0.00412493647091472</v>
+        <v>-0.004124935826256948</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>-0.412493647091472</v>
+        <v>-0.4124935826256948</v>
       </c>
     </row>
     <row r="64">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>24.30820465087891</v>
+        <v>24.30820846557617</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -2628,10 +2628,10 @@
         <v>27.20470428466797</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1191572835340735</v>
+        <v>0.1191571079042555</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>11.91572835340735</v>
+        <v>11.91571079042555</v>
       </c>
     </row>
     <row r="65">
@@ -2659,13 +2659,13 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>18.49174118041992</v>
+        <v>18.49174308776855</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-0.3202741339540492</v>
+        <v>-0.3202740638430636</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>-32.02741339540493</v>
+        <v>-32.02740638430635</v>
       </c>
     </row>
     <row r="66">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>18.49174118041992</v>
+        <v>18.49174308776855</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18.61637115478516</v>
+        <v>18.61637306213379</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.006739764154670258</v>
+        <v>0.006739763459490788</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.6739764154670258</v>
+        <v>0.6739763459490788</v>
       </c>
     </row>
     <row r="67">
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>18.61637115478516</v>
+        <v>18.61637306213379</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>15.11703109741211</v>
+        <v>15.11703300476074</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.1879711157603117</v>
+        <v>-0.1879710965016489</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>-18.79711157603117</v>
+        <v>-18.79710965016489</v>
       </c>
     </row>
     <row r="68">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>15.11703109741211</v>
+        <v>15.11703300476074</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.11271476745605</v>
+        <v>18.11271095275879</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1981661379632127</v>
+        <v>0.1981657344436987</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>19.81661379632127</v>
+        <v>19.81657344436987</v>
       </c>
     </row>
     <row r="69">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>18.11271476745605</v>
+        <v>18.11271095275879</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -2795,13 +2795,13 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>15.05221176147461</v>
+        <v>15.05221080780029</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.1689698670395005</v>
+        <v>-0.1689697446694109</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>-16.89698670395004</v>
+        <v>-16.8969744669411</v>
       </c>
     </row>
     <row r="70">
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>15.05221176147461</v>
+        <v>15.05221080780029</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -2829,13 +2829,13 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>12.10898971557617</v>
+        <v>12.10899066925049</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-0.1955341907580299</v>
+        <v>-0.1955340764311234</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>-19.55341907580299</v>
+        <v>-19.55340764311234</v>
       </c>
     </row>
     <row r="71">
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>12.10898971557617</v>
+        <v>12.10899066925049</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -2866,10 +2866,10 @@
         <v>13.46363162994385</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1118707626471229</v>
+        <v>0.1118706750789171</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>11.18707626471229</v>
+        <v>11.18706750789171</v>
       </c>
     </row>
     <row r="72">
@@ -2897,13 +2897,13 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>16.8854808807373</v>
+        <v>16.88548278808594</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2541549965748526</v>
+        <v>0.2541551382415801</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>25.41549965748526</v>
+        <v>25.41551382415801</v>
       </c>
     </row>
     <row r="73">
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>16.8854808807373</v>
+        <v>16.88548278808594</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
@@ -2934,10 +2934,10 @@
         <v>14.58159923553467</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>-0.1364415773216663</v>
+        <v>-0.13644167486741</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>-13.64415773216663</v>
+        <v>-13.644167486741</v>
       </c>
     </row>
     <row r="74">
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>27.69218254089355</v>
+        <v>27.69218063354492</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>-0.001008096561490035</v>
+        <v>-0.001008165368845293</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>-0.1008096561490035</v>
+        <v>-0.1008165368845293</v>
       </c>
     </row>
     <row r="78">
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>27.69218254089355</v>
+        <v>27.69218063354492</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -3104,10 +3104,10 @@
         <v>37.75653076171875</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.3634364393620109</v>
+        <v>0.3634365332711422</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>36.34364393620109</v>
+        <v>36.34365332711423</v>
       </c>
     </row>
     <row r="79">
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>42.21974945068359</v>
+        <v>42.21975326538086</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.1182105081934617</v>
+        <v>0.1182106092275659</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>11.82105081934617</v>
+        <v>11.82106092275659</v>
       </c>
     </row>
     <row r="80">
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>42.21974945068359</v>
+        <v>42.21975326538086</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -3172,10 +3172,10 @@
         <v>46.63813781738281</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.1046521692853788</v>
+        <v>0.1046520694763253</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>10.46521692853788</v>
+        <v>10.46520694763253</v>
       </c>
     </row>
     <row r="81">
@@ -3203,13 +3203,13 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>49.25904083251953</v>
+        <v>49.2590446472168</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05619656225124547</v>
+        <v>0.05619664404476143</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>5.619656225124547</v>
+        <v>5.619664404476143</v>
       </c>
     </row>
     <row r="82">
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>49.25904083251953</v>
+        <v>49.2590446472168</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
@@ -3240,10 +3240,10 @@
         <v>43.41799926757812</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-0.1185780613309324</v>
+        <v>-0.1185781295896224</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>-11.85780613309324</v>
+        <v>-11.85781295896224</v>
       </c>
     </row>
     <row r="83">
@@ -3339,13 +3339,13 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>49.43413543701172</v>
+        <v>49.43412780761719</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05893429659056126</v>
+        <v>0.05893413316042428</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>5.893429659056126</v>
+        <v>5.893413316042428</v>
       </c>
     </row>
     <row r="86">
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>49.43413543701172</v>
+        <v>49.43412780761719</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -3376,10 +3376,10 @@
         <v>61.41783142089844</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.2424174283204805</v>
+        <v>0.242417620068432</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>24.24174283204805</v>
+        <v>24.2417620068432</v>
       </c>
     </row>
     <row r="87">
@@ -3441,13 +3441,13 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>90.19990539550781</v>
+        <v>90.19991302490234</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.1421810709527707</v>
+        <v>0.1421811675620739</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>14.21810709527707</v>
+        <v>14.21811675620739</v>
       </c>
     </row>
     <row r="89">
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>90.19990539550781</v>
+        <v>90.19991302490234</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -3475,13 +3475,13 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>86.25274658203125</v>
+        <v>86.25273895263672</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>-0.04376012143437502</v>
+        <v>-0.0437602868993443</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>-4.376012143437502</v>
+        <v>-4.37602868993443</v>
       </c>
     </row>
     <row r="90">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>86.25274658203125</v>
+        <v>86.25273895263672</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>109.4436187744141</v>
+        <v>109.443603515625</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.2688711155456016</v>
+        <v>0.2688710508743717</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>26.88711155456016</v>
+        <v>26.88710508743717</v>
       </c>
     </row>
     <row r="91">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>109.4436187744141</v>
+        <v>109.443603515625</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -3543,13 +3543,13 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>123.3367080688477</v>
+        <v>123.3367233276367</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.1269428903211811</v>
+        <v>0.1269431868627044</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>12.69428903211811</v>
+        <v>12.69431868627045</v>
       </c>
     </row>
     <row r="92">
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>123.3367080688477</v>
+        <v>123.3367233276367</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -3580,10 +3580,10 @@
         <v>116.8274383544922</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-0.05277641844244729</v>
+        <v>-0.05277653562964368</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>-5.277641844244729</v>
+        <v>-5.277653562964368</v>
       </c>
     </row>
     <row r="93">
@@ -3611,13 +3611,13 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>119.1735763549805</v>
+        <v>119.173583984375</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02008208031891745</v>
+        <v>0.02008214562373478</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>2.008208031891745</v>
+        <v>2.008214562373478</v>
       </c>
     </row>
     <row r="94">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>119.1735763549805</v>
+        <v>119.173583984375</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -3645,13 +3645,13 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>121.2505340576172</v>
+        <v>121.2505416870117</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.01742800515149523</v>
+        <v>0.01742800403576883</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>1.742800515149523</v>
+        <v>1.742800403576883</v>
       </c>
     </row>
     <row r="95">
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>121.2505340576172</v>
+        <v>121.2505416870117</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>132.5528869628906</v>
+        <v>132.5528717041016</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.09321487111885762</v>
+        <v>0.09321467648585813</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>9.321487111885762</v>
+        <v>9.321467648585813</v>
       </c>
     </row>
     <row r="96">
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>132.5528869628906</v>
+        <v>132.5528717041016</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -3716,10 +3716,10 @@
         <v>138.0343170166016</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.04135277759167555</v>
+        <v>0.04135289746672743</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>4.135277759167555</v>
+        <v>4.135289746672743</v>
       </c>
     </row>
     <row r="97">
@@ -3747,13 +3747,13 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>134.0897369384766</v>
+        <v>134.0897216796875</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>-0.02857680729967016</v>
+        <v>-0.02857691784311611</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>-2.857680729967016</v>
+        <v>-2.857691784311611</v>
       </c>
     </row>
     <row r="98">
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>134.0897369384766</v>
+        <v>134.0897216796875</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -3781,13 +3781,13 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>119.8909454345703</v>
+        <v>119.8909378051758</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-0.1058902182082808</v>
+        <v>-0.1058901733604136</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>-10.58902182082808</v>
+        <v>-10.58901733604136</v>
       </c>
     </row>
     <row r="99">
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>119.8909454345703</v>
+        <v>119.8909378051758</v>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
@@ -3815,13 +3815,13 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>124.7337112426758</v>
+        <v>124.7337036132812</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.04039309049196182</v>
+        <v>0.04039309306242167</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>4.039309049196182</v>
+        <v>4.039309306242167</v>
       </c>
     </row>
     <row r="100">
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>124.7337112426758</v>
+        <v>124.7337036132812</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -3852,10 +3852,10 @@
         <v>108.2283248901367</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-0.1323249840648691</v>
+        <v>-0.1323249309931265</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>-13.23249840648691</v>
+        <v>-13.23249309931265</v>
       </c>
     </row>
     <row r="101">
@@ -3917,13 +3917,13 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>134.9409027099609</v>
+        <v>134.9408874511719</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.2406355273027898</v>
+        <v>0.240635387014742</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>24.06355273027898</v>
+        <v>24.0635387014742</v>
       </c>
     </row>
     <row r="103">
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>134.9409027099609</v>
+        <v>134.9408874511719</v>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
@@ -3954,10 +3954,10 @@
         <v>157.7798614501953</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.1692515633256428</v>
+        <v>0.1692516955417807</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>16.92515633256428</v>
+        <v>16.92516955417807</v>
       </c>
     </row>
     <row r="104">

--- a/isolated_excel/NVIDIA Returns - Current.xlsx
+++ b/isolated_excel/NVIDIA Returns - Current.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Returns" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Returns" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Returns'!$A$1:$H$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Returns'!$A$1:$H$116</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Source and Method'!$A$1:$B$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H115"/>
+  <dimension ref="A1:H116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.625490665435791</v>
+        <v>2.625491619110107</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.685507774353027</v>
+        <v>2.685507535934448</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.02285938765936324</v>
+        <v>0.02285892531040834</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>2.285938765936324</v>
+        <v>2.285892531040834</v>
       </c>
     </row>
     <row r="3">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.685507774353027</v>
+        <v>2.685507535934448</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.49925971031189</v>
+        <v>2.499259948730469</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.06935301614831746</v>
+        <v>-0.06935284474603898</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-6.935301614831745</v>
+        <v>-6.935284474603898</v>
       </c>
     </row>
     <row r="4">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.49925971031189</v>
+        <v>2.499259948730469</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.682739973068237</v>
+        <v>2.682739496231079</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.07341384410724183</v>
+        <v>0.07341355091686697</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>7.341384410724183</v>
+        <v>7.341355091686697</v>
       </c>
     </row>
     <row r="5">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.682739973068237</v>
+        <v>2.682739496231079</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.56871223449707</v>
+        <v>2.568711757659912</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.04250420827805912</v>
+        <v>-0.04250421583286856</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-4.250420827805912</v>
+        <v>-4.250421583286856</v>
       </c>
     </row>
     <row r="6">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.56871223449707</v>
+        <v>2.568711757659912</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -656,10 +656,10 @@
         <v>3.558812141418457</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3854460198478553</v>
+        <v>0.3854462770320806</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>38.54460198478553</v>
+        <v>38.54462770320806</v>
       </c>
     </row>
     <row r="7">
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.563989400863647</v>
+        <v>3.563990116119385</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.00145477177200104</v>
+        <v>0.001454972753595296</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.145477177200104</v>
+        <v>0.1454972753595296</v>
       </c>
     </row>
     <row r="8">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.563989400863647</v>
+        <v>3.563990116119385</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         <v>4.006528377532959</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1241695546462829</v>
+        <v>0.1241693290371488</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12.41695546462829</v>
+        <v>12.41693290371488</v>
       </c>
     </row>
     <row r="9">
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.181059837341309</v>
+        <v>4.181058406829834</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.04356176803515321</v>
+        <v>0.04356141099001598</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>4.356176803515321</v>
+        <v>4.356141099001598</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4.181059837341309</v>
+        <v>4.181058406829834</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4.411284923553467</v>
+        <v>4.41128396987915</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05506381041381037</v>
+        <v>0.05506394330039477</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>5.506381041381037</v>
+        <v>5.506394330039477</v>
       </c>
     </row>
     <row r="11">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.411284923553467</v>
+        <v>4.41128396987915</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -823,13 +823,13 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5.103194236755371</v>
+        <v>5.10319185256958</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1568498351823857</v>
+        <v>0.1568495448071063</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>15.68498351823857</v>
+        <v>15.68495448071063</v>
       </c>
     </row>
     <row r="12">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>5.103194236755371</v>
+        <v>5.10319185256958</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4.956110000610352</v>
+        <v>4.956111907958984</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-0.02882199448448508</v>
+        <v>-0.02882116699895132</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>-2.882199448448508</v>
+        <v>-2.882116699895132</v>
       </c>
     </row>
     <row r="13">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4.956110000610352</v>
+        <v>4.956111907958984</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -891,13 +891,13 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4.778075695037842</v>
+        <v>4.778077125549316</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.03592218605934583</v>
+        <v>-0.03592226844671587</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-3.592218605934583</v>
+        <v>-3.592226844671587</v>
       </c>
     </row>
     <row r="14">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.778075695037842</v>
+        <v>4.778077125549316</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6.069513320922852</v>
+        <v>6.069514274597168</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2702840449401422</v>
+        <v>0.270283864222761</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>27.02840449401423</v>
+        <v>27.0283864222761</v>
       </c>
     </row>
     <row r="15">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6.069513320922852</v>
+        <v>6.069514274597168</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5.979395389556885</v>
+        <v>5.979394912719727</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.01484763713349335</v>
+        <v>-0.01484787048851988</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>-1.484763713349335</v>
+        <v>-1.484787048851988</v>
       </c>
     </row>
     <row r="16">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.979395389556885</v>
+        <v>5.979394912719727</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5.722182750701904</v>
+        <v>5.722182273864746</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.04301649616685432</v>
+        <v>-0.04301649959727905</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-4.301649616685433</v>
+        <v>-4.301649959727905</v>
       </c>
     </row>
     <row r="17">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5.722182750701904</v>
+        <v>5.722182273864746</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -1027,13 +1027,13 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.556884765625</v>
+        <v>5.556884288787842</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02888722578051672</v>
+        <v>-0.02888722818772815</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-2.888722578051672</v>
+        <v>-2.888722818772815</v>
       </c>
     </row>
     <row r="18">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5.556884765625</v>
+        <v>5.556884288787842</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>6.235026836395264</v>
+        <v>6.235025405883789</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1220363745826194</v>
+        <v>0.1220362134342508</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.20363745826194</v>
+        <v>12.20362134342508</v>
       </c>
     </row>
     <row r="19">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6.235026836395264</v>
+        <v>6.235025405883789</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.857002258300781</v>
+        <v>5.857003688812256</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-0.06062918220140889</v>
+        <v>-0.06062873724857742</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>-6.062918220140889</v>
+        <v>-6.062873724857742</v>
       </c>
     </row>
     <row r="20">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.857002258300781</v>
+        <v>5.857003688812256</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -1132,10 +1132,10 @@
         <v>6.053802013397217</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.03360076476281404</v>
+        <v>0.03360051231671157</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3.360076476281404</v>
+        <v>3.360051231671157</v>
       </c>
     </row>
     <row r="21">
@@ -1197,13 +1197,13 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>6.951605796813965</v>
+        <v>6.951604843139648</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.001211391988220623</v>
+        <v>0.001211254634403636</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.1211391988220623</v>
+        <v>0.1211254634403636</v>
       </c>
     </row>
     <row r="23">
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.951605796813965</v>
+        <v>6.951604843139648</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1231,13 +1231,13 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5.215310573577881</v>
+        <v>5.215311527252197</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-0.2497689417360024</v>
+        <v>-0.2497687016259206</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>-24.97689417360024</v>
+        <v>-24.97687016259206</v>
       </c>
     </row>
     <row r="24">
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>5.215310573577881</v>
+        <v>5.215311527252197</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -1265,13 +1265,13 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>4.046821117401123</v>
+        <v>4.046820640563965</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-0.2240498316814782</v>
+        <v>-0.2240500650023255</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>-22.40498316814782</v>
+        <v>-22.40500650023255</v>
       </c>
     </row>
     <row r="25">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4.046821117401123</v>
+        <v>4.046820640563965</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.305700063705444</v>
+        <v>3.305699825286865</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-0.1831365983806144</v>
+        <v>-0.1831365610445778</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>-18.31365983806144</v>
+        <v>-18.31365610445778</v>
       </c>
     </row>
     <row r="26">
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3.305700063705444</v>
+        <v>3.305699825286865</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -1333,13 +1333,13 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3.559508323669434</v>
+        <v>3.559507608413696</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.0767789742180931</v>
+        <v>0.0767788355086978</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>7.67789742180931</v>
+        <v>7.67788355086978</v>
       </c>
     </row>
     <row r="27">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.559508323669434</v>
+        <v>3.559507608413696</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -1367,13 +1367,13 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.823692321777344</v>
+        <v>3.823692083358765</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.07421923875024605</v>
+        <v>0.074219387625583</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>7.421923875024605</v>
+        <v>7.4219387625583</v>
       </c>
     </row>
     <row r="28">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.823692321777344</v>
+        <v>3.823692083358765</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -1404,10 +1404,10 @@
         <v>4.450810432434082</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.164008517914757</v>
+        <v>0.1640085904941517</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>16.4008517914757</v>
+        <v>16.40085904941517</v>
       </c>
     </row>
     <row r="29">
@@ -1435,13 +1435,13 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.486504554748535</v>
+        <v>4.486504077911377</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.008019690538680679</v>
+        <v>0.008019583403774622</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.8019690538680679</v>
+        <v>0.8019583403774622</v>
       </c>
     </row>
     <row r="30">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.486504554748535</v>
+        <v>4.486504077911377</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -1472,10 +1472,10 @@
         <v>3.361522197723389</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.2507480697494133</v>
+        <v>-0.2507479901169969</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-25.07480697494133</v>
+        <v>-25.07479901169969</v>
       </c>
     </row>
     <row r="31">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.075469017028809</v>
+        <v>4.075468063354492</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2123879532281372</v>
+        <v>0.2123876695250229</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>21.23879532281372</v>
+        <v>21.23876695250229</v>
       </c>
     </row>
     <row r="32">
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>4.075469017028809</v>
+        <v>4.075468063354492</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -1540,10 +1540,10 @@
         <v>4.186890125274658</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.02733945658285974</v>
+        <v>0.02733969698402072</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>2.733945658285974</v>
+        <v>2.733969698402072</v>
       </c>
     </row>
     <row r="33">
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4.1609787940979</v>
+        <v>4.160977840423584</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.006188681909835902</v>
+        <v>-0.006188909686129951</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>-0.6188681909835902</v>
+        <v>-0.6188909686129951</v>
       </c>
     </row>
     <row r="34">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>4.1609787940979</v>
+        <v>4.160977840423584</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -1605,13 +1605,13 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>4.323929786682129</v>
+        <v>4.323929309844971</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.03916169743892106</v>
+        <v>0.03916182101195664</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>3.916169743892106</v>
+        <v>3.916182101195664</v>
       </c>
     </row>
     <row r="35">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>4.323929786682129</v>
+        <v>4.323929309844971</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -1642,10 +1642,10 @@
         <v>4.993371963500977</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1548226289151955</v>
+        <v>0.1548227562674951</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>15.48226289151955</v>
+        <v>15.48227562674951</v>
       </c>
     </row>
     <row r="36">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.387831687927246</v>
+        <v>5.387832641601562</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.07899666343896872</v>
+        <v>0.07899685442700721</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>7.899666343896872</v>
+        <v>7.899685442700721</v>
       </c>
     </row>
     <row r="37">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.387831687927246</v>
+        <v>5.387832641601562</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -1710,10 +1710,10 @@
         <v>5.849205493927002</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.08563255734836273</v>
+        <v>0.08563236518577044</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>8.563255734836272</v>
+        <v>8.563236518577044</v>
       </c>
     </row>
     <row r="38">
@@ -1741,13 +1741,13 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>5.877296924591064</v>
+        <v>5.877295970916748</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.004802606216045779</v>
+        <v>0.00480244317265166</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.4802606216045779</v>
+        <v>0.480244317265166</v>
       </c>
     </row>
     <row r="39">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>5.877296924591064</v>
+        <v>5.877295970916748</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>6.717551231384277</v>
+        <v>6.717550277709961</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.1429661147929286</v>
+        <v>0.1429661379912008</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>14.29661147929286</v>
+        <v>14.29661379912008</v>
       </c>
     </row>
     <row r="40">
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>6.717551231384277</v>
+        <v>6.717550277709961</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>6.556621074676514</v>
+        <v>6.556621551513672</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.02395666979894417</v>
+        <v>-0.02395646024865339</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>-2.395666979894417</v>
+        <v>-2.395646024865339</v>
       </c>
     </row>
     <row r="41">
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6.556621074676514</v>
+        <v>6.556621551513672</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         <v>7.269989967346191</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1088012994108971</v>
+        <v>0.1088012187721632</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>10.88012994108971</v>
+        <v>10.88012187721632</v>
       </c>
     </row>
     <row r="42">
@@ -1945,13 +1945,13 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.56580543518066</v>
+        <v>10.56580352783203</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1176068331579609</v>
+        <v>0.1176066314065773</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>11.76068331579609</v>
+        <v>11.76066314065773</v>
       </c>
     </row>
     <row r="45">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10.56580543518066</v>
+        <v>10.56580352783203</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -1979,13 +1979,13 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13.31282997131348</v>
+        <v>13.31283283233643</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2599919668202599</v>
+        <v>0.2599924650565644</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>25.99919668202599</v>
+        <v>25.99924650565644</v>
       </c>
     </row>
     <row r="46">
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>13.31282997131348</v>
+        <v>13.31283283233643</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>13.47213745117188</v>
+        <v>13.47213935852051</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.01196646244274691</v>
+        <v>0.01196638823535223</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>1.196646244274691</v>
+        <v>1.196638823535223</v>
       </c>
     </row>
     <row r="47">
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>13.47213745117188</v>
+        <v>13.47213935852051</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -2047,13 +2047,13 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>12.47993755340576</v>
+        <v>12.47993659973145</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>-0.07364829087902502</v>
+        <v>-0.07364849281799779</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>-7.364829087902502</v>
+        <v>-7.364849281799779</v>
       </c>
     </row>
     <row r="48">
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>12.47993755340576</v>
+        <v>12.47993659973145</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.34369659423828</v>
+        <v>13.34369564056396</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.0692118079226125</v>
+        <v>0.06921181321154357</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>6.92118079226125</v>
+        <v>6.921181321154357</v>
       </c>
     </row>
     <row r="49">
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>13.34369659423828</v>
+        <v>13.34369564056396</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>13.00253105163574</v>
+        <v>13.00253200531006</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>-0.0255675434609216</v>
+        <v>-0.02556740234817645</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>-2.55675434609216</v>
+        <v>-2.556740234817645</v>
       </c>
     </row>
     <row r="50">
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>13.00253105163574</v>
+        <v>13.00253200531006</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>12.93754291534424</v>
+        <v>12.93754100799561</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-0.004998114292780631</v>
+        <v>-0.004998333962024648</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>-0.4998114292780631</v>
+        <v>-0.4998333962024648</v>
       </c>
     </row>
     <row r="51">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>12.93754291534424</v>
+        <v>12.93754100799561</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>13.65937995910645</v>
+        <v>13.65938186645508</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.05579398255800871</v>
+        <v>0.05579428563846589</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>5.579398255800871</v>
+        <v>5.579428563846589</v>
       </c>
     </row>
     <row r="52">
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>13.65937995910645</v>
+        <v>13.65938186645508</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>13.29919147491455</v>
+        <v>13.29919242858887</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-0.02636931436640821</v>
+        <v>-0.02636938050255189</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>-2.636931436640821</v>
+        <v>-2.636938050255189</v>
       </c>
     </row>
     <row r="53">
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>13.29919147491455</v>
+        <v>13.29919242858887</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -2251,13 +2251,13 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14.95433521270752</v>
+        <v>14.9543342590332</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1244544633344791</v>
+        <v>0.1244543109915703</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>12.44544633344791</v>
+        <v>12.44543109915703</v>
       </c>
     </row>
     <row r="54">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>14.95433521270752</v>
+        <v>14.9543342590332</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -2288,10 +2288,10 @@
         <v>16.18479537963867</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.08228116793085949</v>
+        <v>0.08228123695056544</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>8.228116793085949</v>
+        <v>8.228123695056544</v>
       </c>
     </row>
     <row r="55">
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>19.93355369567871</v>
+        <v>19.93355178833008</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2316222249405868</v>
+        <v>0.2316221070924096</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>23.16222249405868</v>
+        <v>23.16221070924096</v>
       </c>
     </row>
     <row r="56">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>19.93355369567871</v>
+        <v>19.93355178833008</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>19.43178939819336</v>
+        <v>19.43178749084473</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.02517184367352054</v>
+        <v>-0.02517184608209688</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>-2.517184367352054</v>
+        <v>-2.517184608209688</v>
       </c>
     </row>
     <row r="57">
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>19.43178939819336</v>
+        <v>19.43178749084473</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>22.31177711486816</v>
+        <v>22.31177139282227</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1482101137295451</v>
+        <v>0.1482099319650567</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>14.82101137295451</v>
+        <v>14.82099319650567</v>
       </c>
     </row>
     <row r="58">
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>22.31177711486816</v>
+        <v>22.31177139282227</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -2424,10 +2424,10 @@
         <v>20.64823150634766</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-0.07455908150910806</v>
+        <v>-0.07455884417181569</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>-7.455908150910806</v>
+        <v>-7.455884417181569</v>
       </c>
     </row>
     <row r="59">
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25.48336410522461</v>
+        <v>25.48336791992188</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2341669114563416</v>
+        <v>0.234167096203266</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>23.41669114563416</v>
+        <v>23.4167096203266</v>
       </c>
     </row>
     <row r="60">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>25.48336410522461</v>
+        <v>25.48336791992188</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>32.5691032409668</v>
+        <v>32.56910705566406</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2780535217596904</v>
+        <v>0.2780534801368559</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>27.80535217596904</v>
+        <v>27.8053480136856</v>
       </c>
     </row>
     <row r="61">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>32.5691032409668</v>
+        <v>32.56910705566406</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>29.31838035583496</v>
+        <v>29.31837844848633</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-0.09981002120570948</v>
+        <v>-0.09981018520470619</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>-9.981002120570947</v>
+        <v>-9.98101852047062</v>
       </c>
     </row>
     <row r="62">
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>29.31838035583496</v>
+        <v>29.31837844848633</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -2557,13 +2557,13 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>24.40889358520508</v>
+        <v>24.40889167785645</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-0.1674542287481032</v>
+        <v>-0.1674542396420752</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>-16.74542287481032</v>
+        <v>-16.74542396420752</v>
       </c>
     </row>
     <row r="63">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>24.40889358520508</v>
+        <v>24.40889167785645</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -2594,10 +2594,10 @@
         <v>24.30820846557617</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-0.004124935826256948</v>
+        <v>-0.004124858007035659</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>-0.4124935826256948</v>
+        <v>-0.4124858007035659</v>
       </c>
     </row>
     <row r="64">
@@ -2625,13 +2625,13 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>27.20470428466797</v>
+        <v>27.20470237731934</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1191571079042555</v>
+        <v>0.1191570294390476</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>11.91571079042555</v>
+        <v>11.91570294390476</v>
       </c>
     </row>
     <row r="65">
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>27.20470428466797</v>
+        <v>27.20470237731934</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -2662,10 +2662,10 @@
         <v>18.49174308776855</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-0.3202740638430636</v>
+        <v>-0.3202740161868048</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>-32.02740638430635</v>
+        <v>-32.02740161868049</v>
       </c>
     </row>
     <row r="66">
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18.61637306213379</v>
+        <v>18.61636734008789</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.006739763459490788</v>
+        <v>0.006739454021604363</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.6739763459490788</v>
+        <v>0.6739454021604363</v>
       </c>
     </row>
     <row r="67">
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>18.61637306213379</v>
+        <v>18.61636734008789</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>15.11703300476074</v>
+        <v>15.11703205108643</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.1879710965016489</v>
+        <v>-0.1879708981389784</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>-18.79710965016489</v>
+        <v>-18.79708981389784</v>
       </c>
     </row>
     <row r="68">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>15.11703300476074</v>
+        <v>15.11703205108643</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.11271095275879</v>
+        <v>18.11271667480469</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1981657344436987</v>
+        <v>0.198166188547769</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>19.81657344436987</v>
+        <v>19.8166188547769</v>
       </c>
     </row>
     <row r="69">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>18.11271095275879</v>
+        <v>18.11271667480469</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -2795,13 +2795,13 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>15.05221080780029</v>
+        <v>15.05221176147461</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.1689697446694109</v>
+        <v>-0.168969954550624</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>-16.8969744669411</v>
+        <v>-16.8969954550624</v>
       </c>
     </row>
     <row r="70">
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>15.05221080780029</v>
+        <v>15.05221176147461</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -2829,13 +2829,13 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>12.10899066925049</v>
+        <v>12.10898876190186</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-0.1955340764311234</v>
+        <v>-0.195534254115783</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>-19.55340764311234</v>
+        <v>-19.5534254115783</v>
       </c>
     </row>
     <row r="71">
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>12.10899066925049</v>
+        <v>12.10898876190186</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -2863,13 +2863,13 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>13.46363162994385</v>
+        <v>13.46363067626953</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1118706750789171</v>
+        <v>0.1118707714577905</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>11.18706750789171</v>
+        <v>11.18707714577905</v>
       </c>
     </row>
     <row r="72">
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>13.46363162994385</v>
+        <v>13.46363067626953</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
         <v>16.88548278808594</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2541551382415801</v>
+        <v>0.2541552270776135</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>25.41551382415801</v>
+        <v>25.41552270776135</v>
       </c>
     </row>
     <row r="73">
@@ -2965,13 +2965,13 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>19.49368667602539</v>
+        <v>19.49368858337402</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.3368689099972106</v>
+        <v>0.3368690408023851</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>33.68689099972107</v>
+        <v>33.68690408023851</v>
       </c>
     </row>
     <row r="75">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>19.49368667602539</v>
+        <v>19.49368858337402</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -3002,10 +3002,10 @@
         <v>23.16452980041504</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1883093324211624</v>
+        <v>0.1883092161517261</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>18.83093324211625</v>
+        <v>18.83092161517261</v>
       </c>
     </row>
     <row r="76">
@@ -3033,13 +3033,13 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>27.72012710571289</v>
+        <v>27.72012519836426</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1966626279293711</v>
+        <v>0.1966625455901805</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>19.6662627929371</v>
+        <v>19.66625455901805</v>
       </c>
     </row>
     <row r="77">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>27.72012710571289</v>
+        <v>27.72012519836426</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>27.69218063354492</v>
+        <v>27.69218254089355</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>-0.001008165368845293</v>
+        <v>-0.001008027823494517</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>-0.1008165368845293</v>
+        <v>-0.1008027823494517</v>
       </c>
     </row>
     <row r="78">
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>27.69218063354492</v>
+        <v>27.69218254089355</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -3104,10 +3104,10 @@
         <v>37.75653076171875</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.3634365332711422</v>
+        <v>0.3634364393620109</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>36.34365332711423</v>
+        <v>36.34364393620109</v>
       </c>
     </row>
     <row r="79">
@@ -3203,13 +3203,13 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>49.2590446472168</v>
+        <v>49.25904083251953</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05619664404476143</v>
+        <v>0.05619656225124547</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>5.619664404476143</v>
+        <v>5.619656225124547</v>
       </c>
     </row>
     <row r="82">
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>49.2590446472168</v>
+        <v>49.25904083251953</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>43.41799926757812</v>
+        <v>43.41800308227539</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-0.1185781295896224</v>
+        <v>-0.1185779838893664</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>-11.85781295896224</v>
+        <v>-11.85779838893664</v>
       </c>
     </row>
     <row r="83">
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>43.41799926757812</v>
+        <v>43.41800308227539</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -3271,13 +3271,13 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>40.70405960083008</v>
+        <v>40.70406341552734</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>-0.06250724843451383</v>
+        <v>-0.06250724294263921</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>-6.250724843451383</v>
+        <v>-6.250724294263921</v>
       </c>
     </row>
     <row r="84">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>40.70405960083008</v>
+        <v>40.70406341552734</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         <v>46.68291091918945</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.1468858727358351</v>
+        <v>0.1468857652521582</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>14.68858727358351</v>
+        <v>14.68857652521582</v>
       </c>
     </row>
     <row r="85">
@@ -3373,13 +3373,13 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>61.41783142089844</v>
+        <v>61.41782760620117</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.242417620068432</v>
+        <v>0.2424175429011504</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>24.2417620068432</v>
+        <v>24.24175429011504</v>
       </c>
     </row>
     <row r="87">
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>61.41783142089844</v>
+        <v>61.41782760620117</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -3407,13 +3407,13 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>78.97163391113281</v>
+        <v>78.97164154052734</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.2858095456014653</v>
+        <v>0.2858097496850216</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>28.58095456014653</v>
+        <v>28.58097496850216</v>
       </c>
     </row>
     <row r="88">
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>78.97163391113281</v>
+        <v>78.97164154052734</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
@@ -3444,10 +3444,10 @@
         <v>90.19991302490234</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.1421811675620739</v>
+        <v>0.1421810572167577</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>14.21811675620739</v>
+        <v>14.21810572167577</v>
       </c>
     </row>
     <row r="89">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>109.443603515625</v>
+        <v>109.4436111450195</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.2688710508743717</v>
+        <v>0.2688711393283107</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>26.88710508743717</v>
+        <v>26.88711393283107</v>
       </c>
     </row>
     <row r="91">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>109.443603515625</v>
+        <v>109.4436111450195</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -3546,10 +3546,10 @@
         <v>123.3367233276367</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.1269431868627044</v>
+        <v>0.1269431083026671</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>12.69431868627045</v>
+        <v>12.69431083026671</v>
       </c>
     </row>
     <row r="92">
@@ -3611,13 +3611,13 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>119.173583984375</v>
+        <v>119.1735763549805</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02008214562373478</v>
+        <v>0.02008208031891745</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>2.008214562373478</v>
+        <v>2.008208031891745</v>
       </c>
     </row>
     <row r="94">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>119.173583984375</v>
+        <v>119.1735763549805</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -3648,10 +3648,10 @@
         <v>121.2505416870117</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.01742800403576883</v>
+        <v>0.01742806917067452</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>1.742800403576883</v>
+        <v>1.742806917067452</v>
       </c>
     </row>
     <row r="95">
@@ -3747,13 +3747,13 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>134.0897216796875</v>
+        <v>134.0897369384766</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>-0.02857691784311611</v>
+        <v>-0.02857680729967016</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>-2.857691784311611</v>
+        <v>-2.857680729967016</v>
       </c>
     </row>
     <row r="98">
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>134.0897216796875</v>
+        <v>134.0897369384766</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -3784,10 +3784,10 @@
         <v>119.8909378051758</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-0.1058901733604136</v>
+        <v>-0.1058902751059577</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>-10.58901733604136</v>
+        <v>-10.58902751059577</v>
       </c>
     </row>
     <row r="99">
@@ -3815,13 +3815,13 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>124.7337036132812</v>
+        <v>124.7337112426758</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.04039309306242167</v>
+        <v>0.04039315669854515</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>4.039309306242167</v>
+        <v>4.039315669854515</v>
       </c>
     </row>
     <row r="100">
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>124.7337036132812</v>
+        <v>124.7337112426758</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -3852,10 +3852,10 @@
         <v>108.2283248901367</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-0.1323249309931265</v>
+        <v>-0.1323249840648691</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>-13.23249309931265</v>
+        <v>-13.23249840648691</v>
       </c>
     </row>
     <row r="101">
@@ -3917,13 +3917,13 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>134.9408874511719</v>
+        <v>134.9409027099609</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.240635387014742</v>
+        <v>0.2406355273027898</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>24.0635387014742</v>
+        <v>24.06355273027898</v>
       </c>
     </row>
     <row r="103">
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>134.9408874511719</v>
+        <v>134.9409027099609</v>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
@@ -3951,13 +3951,13 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>157.7798614501953</v>
+        <v>157.7798461914062</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.1692516955417807</v>
+        <v>0.1692514502480753</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>16.92516955417807</v>
+        <v>16.92514502480753</v>
       </c>
     </row>
     <row r="104">
@@ -3977,7 +3977,7 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>157.7798614501953</v>
+        <v>157.7798461914062</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>177.6334075927734</v>
+        <v>177.6334228515625</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.1258306729394936</v>
+        <v>0.1258308785272324</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>12.58306729394936</v>
+        <v>12.58308785272324</v>
       </c>
     </row>
     <row r="105">
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>177.6334075927734</v>
+        <v>177.6334228515625</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -4019,13 +4019,13 @@
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>173.9483184814453</v>
+        <v>173.9483032226562</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>-0.02074547328268472</v>
+        <v>-0.02074564330151807</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>-2.074547328268472</v>
+        <v>-2.074564330151807</v>
       </c>
     </row>
     <row r="106">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>173.9483184814453</v>
+        <v>173.9483032226562</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
@@ -4056,10 +4056,10 @@
         <v>186.3423309326172</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.07125111963927333</v>
+        <v>0.07125121360969189</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>7.125111963927333</v>
+        <v>7.125121360969189</v>
       </c>
     </row>
     <row r="107">
@@ -4368,8 +4368,42 @@
         <v>-5.123049341072095</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>200.0899963378906</v>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>200.75</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>0.003298534030631073</v>
+      </c>
+      <c r="H116" s="3" t="n">
+        <v>0.3298534030631073</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H115"/>
+  <autoFilter ref="A1:H116"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4419,7 +4453,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Jun 2026; 114 monthly observations</t>
+          <t>Jan 2017 to Jul 2026; 115 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/NVIDIA Returns - Current.xlsx
+++ b/isolated_excel/NVIDIA Returns - Current.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Returns" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Returns" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Returns'!$A$1:$H$116</definedName>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.625491619110107</v>
+        <v>2.62549090385437</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.685507535934448</v>
+        <v>2.685508012771606</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.02285892531040834</v>
+        <v>0.02285938558352174</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>2.285892531040834</v>
+        <v>2.285938558352174</v>
       </c>
     </row>
     <row r="3">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.685507535934448</v>
+        <v>2.685508012771606</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.499259948730469</v>
+        <v>2.499260425567627</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.06935284474603898</v>
+        <v>-0.06935283243179036</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-6.935284474603898</v>
+        <v>-6.935283243179036</v>
       </c>
     </row>
     <row r="4">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.499259948730469</v>
+        <v>2.499260425567627</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.682739496231079</v>
+        <v>2.682739734649658</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.07341355091686697</v>
+        <v>0.0734134415145471</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>7.341355091686697</v>
+        <v>7.34134415145471</v>
       </c>
     </row>
     <row r="5">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.682739496231079</v>
+        <v>2.682739734649658</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.568711757659912</v>
+        <v>2.568711996078491</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.04250421583286856</v>
+        <v>-0.04250421205546351</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-4.250421583286856</v>
+        <v>-4.250421205546351</v>
       </c>
     </row>
     <row r="6">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.568711757659912</v>
+        <v>2.568711996078491</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -653,13 +653,13 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3.558812141418457</v>
+        <v>3.558812379837036</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3854462770320806</v>
+        <v>0.3854462412563477</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>38.54462770320806</v>
+        <v>38.54462412563478</v>
       </c>
     </row>
     <row r="7">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.558812141418457</v>
+        <v>3.558812379837036</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.563990116119385</v>
+        <v>3.56398868560791</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.001454972753595296</v>
+        <v>0.001454503699099385</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.1454972753595296</v>
+        <v>0.1454503699099385</v>
       </c>
     </row>
     <row r="8">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.563990116119385</v>
+        <v>3.56398868560791</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -721,13 +721,13 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4.006528377532959</v>
+        <v>4.006528854370117</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1241693290371488</v>
+        <v>0.1241699140486252</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12.41693290371488</v>
+        <v>12.41699140486252</v>
       </c>
     </row>
     <row r="9">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4.006528377532959</v>
+        <v>4.006528854370117</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.181058406829834</v>
+        <v>4.181059837341309</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.04356141099001598</v>
+        <v>0.04356164383561634</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>4.356141099001598</v>
+        <v>4.356164383561634</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4.181058406829834</v>
+        <v>4.181059837341309</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4.41128396987915</v>
+        <v>4.411285400390625</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05506394330039477</v>
+        <v>0.05506392446076891</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>5.506394330039477</v>
+        <v>5.506392446076891</v>
       </c>
     </row>
     <row r="11">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.41128396987915</v>
+        <v>4.411285400390625</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -823,13 +823,13 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5.10319185256958</v>
+        <v>5.103194236755371</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1568495448071063</v>
+        <v>0.1568497101328961</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>15.68495448071063</v>
+        <v>15.6849710132896</v>
       </c>
     </row>
     <row r="12">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>5.10319185256958</v>
+        <v>5.103194236755371</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4.956111907958984</v>
+        <v>4.956111431121826</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-0.02882116699895132</v>
+        <v>-0.02882171416760748</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>-2.882116699895132</v>
+        <v>-2.882171416760748</v>
       </c>
     </row>
     <row r="13">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4.956111907958984</v>
+        <v>4.956111431121826</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -891,13 +891,13 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4.778077125549316</v>
+        <v>4.778075218200684</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.03592226844671587</v>
+        <v>-0.03592256053872533</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-3.592226844671587</v>
+        <v>-3.592256053872533</v>
       </c>
     </row>
     <row r="14">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.778077125549316</v>
+        <v>4.778075218200684</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6.069514274597168</v>
+        <v>6.069513320922852</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.270283864222761</v>
+        <v>0.2702841717105691</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>27.0283864222761</v>
+        <v>27.02841717105691</v>
       </c>
     </row>
     <row r="15">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6.069514274597168</v>
+        <v>6.069513320922852</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5.979394912719727</v>
+        <v>5.979395866394043</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.01484787048851988</v>
+        <v>-0.01484755857082565</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>-1.484787048851988</v>
+        <v>-1.484755857082565</v>
       </c>
     </row>
     <row r="16">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.979394912719727</v>
+        <v>5.979395866394043</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5.722182273864746</v>
+        <v>5.722181797027588</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.04301649959727905</v>
+        <v>-0.0430167319765653</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-4.301649959727905</v>
+        <v>-4.30167319765653</v>
       </c>
     </row>
     <row r="17">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5.722182273864746</v>
+        <v>5.722181797027588</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -1027,13 +1027,13 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.556884288787842</v>
+        <v>5.556883811950684</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02888722818772815</v>
+        <v>-0.02888723059494003</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-2.888722818772815</v>
+        <v>-2.888723059494003</v>
       </c>
     </row>
     <row r="18">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5.556884288787842</v>
+        <v>5.556883811950684</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -1064,10 +1064,10 @@
         <v>6.235025405883789</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1220362134342508</v>
+        <v>0.1220363097163717</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.20362134342508</v>
+        <v>12.20363097163717</v>
       </c>
     </row>
     <row r="19">
@@ -1197,13 +1197,13 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>6.951604843139648</v>
+        <v>6.951605796813965</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.001211254634403636</v>
+        <v>0.001211391988220623</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.1211254634403636</v>
+        <v>0.1211391988220623</v>
       </c>
     </row>
     <row r="23">
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.951604843139648</v>
+        <v>6.951605796813965</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1234,10 +1234,10 @@
         <v>5.215311527252197</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-0.2497687016259206</v>
+        <v>-0.2497688045483735</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>-24.97687016259206</v>
+        <v>-24.97688045483735</v>
       </c>
     </row>
     <row r="24">
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.305699825286865</v>
+        <v>3.305700540542603</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-0.1831365610445778</v>
+        <v>-0.1831363842994731</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>-18.31365610445778</v>
+        <v>-18.31363842994731</v>
       </c>
     </row>
     <row r="26">
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3.305699825286865</v>
+        <v>3.305700540542603</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -1333,13 +1333,13 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3.559507608413696</v>
+        <v>3.559508323669434</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.0767788355086978</v>
+        <v>0.07677881889603055</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>7.67788355086978</v>
+        <v>7.677881889603055</v>
       </c>
     </row>
     <row r="27">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.559507608413696</v>
+        <v>3.559508323669434</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -1367,13 +1367,13 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.823692083358765</v>
+        <v>3.823691368103027</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.074219387625583</v>
+        <v>0.07421897082719897</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>7.4219387625583</v>
+        <v>7.421897082719897</v>
       </c>
     </row>
     <row r="28">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.823692083358765</v>
+        <v>3.823691368103027</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -1404,10 +1404,10 @@
         <v>4.450810432434082</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1640085904941517</v>
+        <v>0.1640088082323901</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>16.40085904941517</v>
+        <v>16.40088082323901</v>
       </c>
     </row>
     <row r="29">
@@ -1435,13 +1435,13 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.486504077911377</v>
+        <v>4.486505031585693</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.008019583403774622</v>
+        <v>0.008019797673586959</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.8019583403774622</v>
+        <v>0.8019797673586959</v>
       </c>
     </row>
     <row r="30">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.486504077911377</v>
+        <v>4.486505031585693</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -1472,10 +1472,10 @@
         <v>3.361522197723389</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.2507479901169969</v>
+        <v>-0.2507481493818129</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-25.07479901169969</v>
+        <v>-25.07481493818129</v>
       </c>
     </row>
     <row r="31">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.075468063354492</v>
+        <v>4.075469017028809</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2123876695250229</v>
+        <v>0.2123879532281372</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>21.23876695250229</v>
+        <v>21.23879532281372</v>
       </c>
     </row>
     <row r="32">
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>4.075468063354492</v>
+        <v>4.075469017028809</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4.186890125274658</v>
+        <v>4.186889171600342</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.02733969698402072</v>
+        <v>0.02733922257928567</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>2.733969698402072</v>
+        <v>2.733922257928567</v>
       </c>
     </row>
     <row r="33">
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>4.186890125274658</v>
+        <v>4.186889171600342</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4.160977840423584</v>
+        <v>4.160976886749268</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.006188909686129951</v>
+        <v>-0.006188911095817207</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>-0.6188909686129951</v>
+        <v>-0.6188911095817207</v>
       </c>
     </row>
     <row r="34">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>4.160977840423584</v>
+        <v>4.160976886749268</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -1608,10 +1608,10 @@
         <v>4.323929309844971</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.03916182101195664</v>
+        <v>0.0391620591824553</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>3.916182101195664</v>
+        <v>3.91620591824553</v>
       </c>
     </row>
     <row r="35">
@@ -1639,13 +1639,13 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.993371963500977</v>
+        <v>4.993372917175293</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1548227562674951</v>
+        <v>0.1548229768248279</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>15.48227562674951</v>
+        <v>15.48229768248279</v>
       </c>
     </row>
     <row r="36">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>4.993371963500977</v>
+        <v>4.993372917175293</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.387832641601562</v>
+        <v>5.387831687927246</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.07899685442700721</v>
+        <v>0.07899645736355199</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>7.899685442700721</v>
+        <v>7.899645736355199</v>
       </c>
     </row>
     <row r="37">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.387832641601562</v>
+        <v>5.387831687927246</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -1707,13 +1707,13 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.849205493927002</v>
+        <v>5.849206924438477</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.08563236518577044</v>
+        <v>0.08563282285618801</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>8.563236518577044</v>
+        <v>8.563282285618801</v>
       </c>
     </row>
     <row r="38">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>5.849205493927002</v>
+        <v>5.849206924438477</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -1744,10 +1744,10 @@
         <v>5.877295970916748</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.00480244317265166</v>
+        <v>0.004802197433110722</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.480244317265166</v>
+        <v>0.4802197433110722</v>
       </c>
     </row>
     <row r="39">
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>6.717550277709961</v>
+        <v>6.717552185058594</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.1429661379912008</v>
+        <v>0.1429664625194604</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>14.29661379912008</v>
+        <v>14.29664625194604</v>
       </c>
     </row>
     <row r="40">
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>6.717550277709961</v>
+        <v>6.717552185058594</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>6.556621551513672</v>
+        <v>6.556621074676514</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.02395646024865339</v>
+        <v>-0.02395680836540848</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>-2.395646024865339</v>
+        <v>-2.395680836540848</v>
       </c>
     </row>
     <row r="41">
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6.556621551513672</v>
+        <v>6.556621074676514</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -1843,13 +1843,13 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>7.269989967346191</v>
+        <v>7.26999044418335</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1088012187721632</v>
+        <v>0.1088013721369481</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>10.88012187721632</v>
+        <v>10.88013721369481</v>
       </c>
     </row>
     <row r="42">
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>7.269989967346191</v>
+        <v>7.26999044418335</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>8.830544471740723</v>
+        <v>8.830543518066406</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2146570368602847</v>
+        <v>0.2146568260115995</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>21.46570368602847</v>
+        <v>21.46568260115995</v>
       </c>
     </row>
     <row r="43">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>8.830544471740723</v>
+        <v>8.830543518066406</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>9.45395565032959</v>
+        <v>9.453957557678223</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.07059713934785017</v>
+        <v>0.07059747096386237</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>7.059713934785017</v>
+        <v>7.059747096386237</v>
       </c>
     </row>
     <row r="44">
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9.45395565032959</v>
+        <v>9.453957557678223</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -1945,13 +1945,13 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.56580352783203</v>
+        <v>10.56580543518066</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1176066314065773</v>
+        <v>0.1176066076792814</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>11.76066314065773</v>
+        <v>11.76066076792814</v>
       </c>
     </row>
     <row r="45">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10.56580352783203</v>
+        <v>10.56580543518066</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -1979,13 +1979,13 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13.31283283233643</v>
+        <v>13.31282806396484</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2599924650565644</v>
+        <v>0.2599917862993668</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>25.99924650565644</v>
+        <v>25.99917862993668</v>
       </c>
     </row>
     <row r="46">
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>13.31283283233643</v>
+        <v>13.31282806396484</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>13.47213935852051</v>
+        <v>13.47214031219482</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.01196638823535223</v>
+        <v>0.01196682233590973</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>1.196638823535223</v>
+        <v>1.196682233590973</v>
       </c>
     </row>
     <row r="47">
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>13.47213935852051</v>
+        <v>13.47214031219482</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -2047,13 +2047,13 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>12.47993659973145</v>
+        <v>12.47994041442871</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>-0.07364849281799779</v>
+        <v>-0.07364827523864081</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>-7.364849281799779</v>
+        <v>-7.364827523864081</v>
       </c>
     </row>
     <row r="48">
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>12.47993659973145</v>
+        <v>12.47994041442871</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.34369564056396</v>
+        <v>13.3436975479126</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06921181321154357</v>
+        <v>0.06921163922267226</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>6.921181321154357</v>
+        <v>6.921163922267226</v>
       </c>
     </row>
     <row r="49">
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>13.34369564056396</v>
+        <v>13.3436975479126</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>13.00253200531006</v>
+        <v>13.00253009796143</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>-0.02556740234817645</v>
+        <v>-0.02556768457364667</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>-2.556740234817645</v>
+        <v>-2.556768457364667</v>
       </c>
     </row>
     <row r="50">
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>13.00253200531006</v>
+        <v>13.00253009796143</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>12.93754100799561</v>
+        <v>12.93754291534424</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-0.004998333962024648</v>
+        <v>-0.004998041314080548</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>-0.4998333962024648</v>
+        <v>-0.4998041314080548</v>
       </c>
     </row>
     <row r="51">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>12.93754100799561</v>
+        <v>12.93754291534424</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>13.65938186645508</v>
+        <v>13.65938091278076</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.05579428563846589</v>
+        <v>0.05579405627172118</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>5.579428563846589</v>
+        <v>5.579405627172118</v>
       </c>
     </row>
     <row r="52">
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>13.65938186645508</v>
+        <v>13.65938091278076</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>13.29919242858887</v>
+        <v>13.29919147491455</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-0.02636938050255189</v>
+        <v>-0.0263693823436163</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>-2.636938050255189</v>
+        <v>-2.63693823436163</v>
       </c>
     </row>
     <row r="53">
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>13.29919242858887</v>
+        <v>13.29919147491455</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -2251,13 +2251,13 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14.9543342590332</v>
+        <v>14.95433521270752</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1244543109915703</v>
+        <v>0.1244544633344791</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>12.44543109915703</v>
+        <v>12.44544633344791</v>
       </c>
     </row>
     <row r="54">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>14.9543342590332</v>
+        <v>14.95433521270752</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>16.18479537963867</v>
+        <v>16.18479347229004</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.08228123695056544</v>
+        <v>0.0822810403859966</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>8.228123695056544</v>
+        <v>8.22810403859966</v>
       </c>
     </row>
     <row r="55">
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>16.18479537963867</v>
+        <v>16.18479347229004</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>19.93355178833008</v>
+        <v>19.93355560302734</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2316221070924096</v>
+        <v>0.2316224879332291</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>23.16221070924096</v>
+        <v>23.16224879332292</v>
       </c>
     </row>
     <row r="56">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>19.93355178833008</v>
+        <v>19.93355560302734</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>19.43178749084473</v>
+        <v>19.43178939819336</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.02517184608209688</v>
+        <v>-0.02517193695026387</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>-2.517184608209688</v>
+        <v>-2.517193695026387</v>
       </c>
     </row>
     <row r="57">
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>19.43178749084473</v>
+        <v>19.43178939819336</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -2390,10 +2390,10 @@
         <v>22.31177139282227</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1482099319650567</v>
+        <v>0.1482098192612498</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>14.82099319650567</v>
+        <v>14.82098192612498</v>
       </c>
     </row>
     <row r="58">
@@ -2421,13 +2421,13 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>20.64823150634766</v>
+        <v>20.64822959899902</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-0.07455884417181569</v>
+        <v>-0.07455892965801925</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>-7.455884417181569</v>
+        <v>-7.455892965801924</v>
       </c>
     </row>
     <row r="59">
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>20.64823150634766</v>
+        <v>20.64822959899902</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25.48336791992188</v>
+        <v>25.48336029052734</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.234167096203266</v>
+        <v>0.2341668407136812</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>23.4167096203266</v>
+        <v>23.41668407136812</v>
       </c>
     </row>
     <row r="60">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>25.48336791992188</v>
+        <v>25.48336029052734</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>32.56910705566406</v>
+        <v>32.5691032409668</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2780534801368559</v>
+        <v>0.2780537130761895</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>27.8053480136856</v>
+        <v>27.80537130761896</v>
       </c>
     </row>
     <row r="61">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>32.56910705566406</v>
+        <v>32.5691032409668</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -2526,10 +2526,10 @@
         <v>29.31837844848633</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-0.09981018520470619</v>
+        <v>-0.0998100797688396</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>-9.98101852047062</v>
+        <v>-9.98100797688396</v>
       </c>
     </row>
     <row r="62">
@@ -2557,13 +2557,13 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>24.40889167785645</v>
+        <v>24.40888595581055</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-0.1674542396420752</v>
+        <v>-0.167454434811324</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>-16.74542396420752</v>
+        <v>-16.7454434811324</v>
       </c>
     </row>
     <row r="63">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>24.40889167785645</v>
+        <v>24.40888595581055</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -2594,10 +2594,10 @@
         <v>24.30820846557617</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-0.004124858007035659</v>
+        <v>-0.004124624549298961</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>-0.4124858007035659</v>
+        <v>-0.4124624549298961</v>
       </c>
     </row>
     <row r="64">
@@ -2625,13 +2625,13 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>27.20470237731934</v>
+        <v>27.20470428466797</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1191570294390476</v>
+        <v>0.1191571079042555</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>11.91570294390476</v>
+        <v>11.91571079042555</v>
       </c>
     </row>
     <row r="65">
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>27.20470237731934</v>
+        <v>27.20470428466797</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -2659,13 +2659,13 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>18.49174308776855</v>
+        <v>18.49174118041992</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-0.3202740161868048</v>
+        <v>-0.3202741339540492</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>-32.02740161868049</v>
+        <v>-32.02741339540493</v>
       </c>
     </row>
     <row r="66">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>18.49174308776855</v>
+        <v>18.49174118041992</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18.61636734008789</v>
+        <v>18.61636924743652</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.006739454021604363</v>
+        <v>0.006739661008697384</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.6739454021604363</v>
+        <v>0.6739661008697384</v>
       </c>
     </row>
     <row r="67">
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>18.61636734008789</v>
+        <v>18.61636924743652</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -2730,10 +2730,10 @@
         <v>15.11703205108643</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.1879708981389784</v>
+        <v>-0.1879709813357917</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>-18.79708981389784</v>
+        <v>-18.79709813357917</v>
       </c>
     </row>
     <row r="68">
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.11271667480469</v>
+        <v>18.11271095275879</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.198166188547769</v>
+        <v>0.19816581003128</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>19.8166188547769</v>
+        <v>19.816581003128</v>
       </c>
     </row>
     <row r="69">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>18.11271667480469</v>
+        <v>18.11271095275879</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -2795,13 +2795,13 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>15.05221176147461</v>
+        <v>15.05220985412598</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.168969954550624</v>
+        <v>-0.1689697973216241</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>-16.8969954550624</v>
+        <v>-16.89697973216241</v>
       </c>
     </row>
     <row r="70">
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>15.05221176147461</v>
+        <v>15.05220985412598</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -2829,13 +2829,13 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>12.10898876190186</v>
+        <v>12.10898971557617</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-0.195534254115783</v>
+        <v>-0.1955340888197248</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>-19.5534254115783</v>
+        <v>-19.55340888197248</v>
       </c>
     </row>
     <row r="71">
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>12.10898876190186</v>
+        <v>12.10898971557617</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -2863,13 +2863,13 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>13.46363067626953</v>
+        <v>13.46363258361816</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1118707714577905</v>
+        <v>0.1118708414046692</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>11.18707714577905</v>
+        <v>11.18708414046692</v>
       </c>
     </row>
     <row r="72">
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>13.46363067626953</v>
+        <v>13.46363258361816</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
         <v>16.88548278808594</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2541552270776135</v>
+        <v>0.2541550494055593</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>25.41552270776135</v>
+        <v>25.41550494055593</v>
       </c>
     </row>
     <row r="73">
@@ -2931,13 +2931,13 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>14.58159923553467</v>
+        <v>14.5816011428833</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>-0.13644167486741</v>
+        <v>-0.1364415619095126</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>-13.644167486741</v>
+        <v>-13.64415619095126</v>
       </c>
     </row>
     <row r="74">
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>14.58159923553467</v>
+        <v>14.5816011428833</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
@@ -2965,13 +2965,13 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>19.49368858337402</v>
+        <v>19.49368667602539</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.3368690408023851</v>
+        <v>0.3368687351278623</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>33.68690408023851</v>
+        <v>33.68687351278623</v>
       </c>
     </row>
     <row r="75">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>19.49368858337402</v>
+        <v>19.49368667602539</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -2999,13 +2999,13 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>23.16452980041504</v>
+        <v>23.16453170776367</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1883092161517261</v>
+        <v>0.1883094302655908</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>18.83092161517261</v>
+        <v>18.83094302655908</v>
       </c>
     </row>
     <row r="76">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>23.16452980041504</v>
+        <v>23.16453170776367</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -3033,13 +3033,13 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>27.72012519836426</v>
+        <v>27.72012138366699</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1966625455901805</v>
+        <v>0.1966622823795958</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>19.66625455901805</v>
+        <v>19.66622823795958</v>
       </c>
     </row>
     <row r="77">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>27.72012519836426</v>
+        <v>27.72012138366699</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>27.69218254089355</v>
+        <v>27.69218063354492</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>-0.001008027823494517</v>
+        <v>-0.00100795915484464</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>-0.1008027823494517</v>
+        <v>-0.100795915484464</v>
       </c>
     </row>
     <row r="78">
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>27.69218254089355</v>
+        <v>27.69218063354492</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -3104,10 +3104,10 @@
         <v>37.75653076171875</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.3634364393620109</v>
+        <v>0.3634365332711422</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>36.34364393620109</v>
+        <v>36.34365332711423</v>
       </c>
     </row>
     <row r="79">
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>42.21975326538086</v>
+        <v>42.21974945068359</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.1182106092275659</v>
+        <v>0.1182105081934617</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>11.82106092275659</v>
+        <v>11.82105081934617</v>
       </c>
     </row>
     <row r="80">
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>42.21975326538086</v>
+        <v>42.21974945068359</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -3169,13 +3169,13 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>46.63813781738281</v>
+        <v>46.63814544677734</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.1046520694763253</v>
+        <v>0.1046523499921483</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>10.46520694763253</v>
+        <v>10.46523499921483</v>
       </c>
     </row>
     <row r="81">
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>46.63813781738281</v>
+        <v>46.63814544677734</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
@@ -3206,10 +3206,10 @@
         <v>49.25904083251953</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05619656225124547</v>
+        <v>0.05619638947121319</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>5.619656225124547</v>
+        <v>5.619638947121319</v>
       </c>
     </row>
     <row r="82">
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>43.41800308227539</v>
+        <v>43.41799926757812</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-0.1185779838893664</v>
+        <v>-0.1185780613309324</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>-11.85779838893664</v>
+        <v>-11.85780613309324</v>
       </c>
     </row>
     <row r="83">
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>43.41800308227539</v>
+        <v>43.41799926757812</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -3274,10 +3274,10 @@
         <v>40.70406341552734</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>-0.06250724294263921</v>
+        <v>-0.06250716057470163</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>-6.250724294263921</v>
+        <v>-6.250716057470163</v>
       </c>
     </row>
     <row r="84">
@@ -3305,13 +3305,13 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>46.68291091918945</v>
+        <v>46.68291473388672</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.1468857652521582</v>
+        <v>0.1468858589700071</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>14.68857652521582</v>
+        <v>14.68858589700071</v>
       </c>
     </row>
     <row r="85">
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>46.68291091918945</v>
+        <v>46.68291473388672</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -3339,13 +3339,13 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>49.43412780761719</v>
+        <v>49.43413162231445</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05893413316042428</v>
+        <v>0.05893412834461786</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>5.893413316042428</v>
+        <v>5.893412834461786</v>
       </c>
     </row>
     <row r="86">
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>49.43412780761719</v>
+        <v>49.43413162231445</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -3373,13 +3373,13 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>61.41782760620117</v>
+        <v>61.41783142089844</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.2424175429011504</v>
+        <v>0.2424175241944488</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>24.24175429011504</v>
+        <v>24.24175241944489</v>
       </c>
     </row>
     <row r="87">
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>61.41782760620117</v>
+        <v>61.41783142089844</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -3407,13 +3407,13 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>78.97164154052734</v>
+        <v>78.97162628173828</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.2858097496850216</v>
+        <v>0.2858094213803009</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>28.58097496850216</v>
+        <v>28.58094213803009</v>
       </c>
     </row>
     <row r="88">
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>78.97164154052734</v>
+        <v>78.97162628173828</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
@@ -3444,10 +3444,10 @@
         <v>90.19991302490234</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.1421810572167577</v>
+        <v>0.1421812779074114</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>14.21810572167577</v>
+        <v>14.21812779074114</v>
       </c>
     </row>
     <row r="89">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>109.4436111450195</v>
+        <v>109.4435958862305</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.2688711393283107</v>
+        <v>0.2688709624204324</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>26.88711393283107</v>
+        <v>26.88709624204324</v>
       </c>
     </row>
     <row r="91">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>109.4436111450195</v>
+        <v>109.4435958862305</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -3543,13 +3543,13 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>123.3367233276367</v>
+        <v>123.3367309570312</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.1269431083026671</v>
+        <v>0.1269433351334972</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>12.69431083026671</v>
+        <v>12.69433351334972</v>
       </c>
     </row>
     <row r="92">
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>123.3367233276367</v>
+        <v>123.3367309570312</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -3580,10 +3580,10 @@
         <v>116.8274383544922</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-0.05277653562964368</v>
+        <v>-0.05277659422323111</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>-5.277653562964368</v>
+        <v>-5.277659422323111</v>
       </c>
     </row>
     <row r="93">
@@ -3645,13 +3645,13 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>121.2505416870117</v>
+        <v>121.2505493164062</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.01742806917067452</v>
+        <v>0.01742813318985359</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>1.742806917067452</v>
+        <v>1.742813318985359</v>
       </c>
     </row>
     <row r="95">
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>121.2505416870117</v>
+        <v>121.2505493164062</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -3682,10 +3682,10 @@
         <v>132.5528717041016</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.09321467648585813</v>
+        <v>0.09321460769799583</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>9.321467648585813</v>
+        <v>9.321460769799582</v>
       </c>
     </row>
     <row r="96">
@@ -3713,13 +3713,13 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>138.0343170166016</v>
+        <v>138.0343322753906</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.04135289746672743</v>
+        <v>0.04135301258146518</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>4.135289746672743</v>
+        <v>4.135301258146518</v>
       </c>
     </row>
     <row r="97">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>138.0343170166016</v>
+        <v>138.0343322753906</v>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
@@ -3750,10 +3750,10 @@
         <v>134.0897369384766</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>-0.02857680729967016</v>
+        <v>-0.02857691468412549</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>-2.857680729967016</v>
+        <v>-2.857691468412549</v>
       </c>
     </row>
     <row r="98">
@@ -3815,13 +3815,13 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>124.7337112426758</v>
+        <v>124.7337036132812</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.04039315669854515</v>
+        <v>0.04039309306242167</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>4.039315669854515</v>
+        <v>4.039309306242167</v>
       </c>
     </row>
     <row r="100">
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>124.7337112426758</v>
+        <v>124.7337036132812</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -3852,10 +3852,10 @@
         <v>108.2283248901367</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-0.1323249840648691</v>
+        <v>-0.1323249309931265</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>-13.23249840648691</v>
+        <v>-13.23249309931265</v>
       </c>
     </row>
     <row r="101">
@@ -3951,13 +3951,13 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>157.7798461914062</v>
+        <v>157.7798614501953</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.1692514502480753</v>
+        <v>0.1692515633256428</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>16.92514502480753</v>
+        <v>16.92515633256428</v>
       </c>
     </row>
     <row r="104">
@@ -3977,7 +3977,7 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>157.7798461914062</v>
+        <v>157.7798614501953</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>177.6334228515625</v>
+        <v>177.6334075927734</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.1258308785272324</v>
+        <v>0.1258306729394936</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>12.58308785272324</v>
+        <v>12.58306729394936</v>
       </c>
     </row>
     <row r="105">
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>177.6334228515625</v>
+        <v>177.6334075927734</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -4022,10 +4022,10 @@
         <v>173.9483032226562</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>-0.02074564330151807</v>
+        <v>-0.02074555918313137</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>-2.074564330151807</v>
+        <v>-2.074555918313137</v>
       </c>
     </row>
     <row r="106">
@@ -4155,13 +4155,13 @@
         </is>
       </c>
       <c r="F109" s="3" t="n">
-        <v>186.2727966308594</v>
+        <v>186.2728118896484</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>0.05373093153479269</v>
+        <v>0.05373101785259271</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>5.373093153479269</v>
+        <v>5.373101785259271</v>
       </c>
     </row>
     <row r="110">
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>186.2727966308594</v>
+        <v>186.2728118896484</v>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
@@ -4192,10 +4192,10 @@
         <v>190.8971710205078</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0.02482581715253174</v>
+        <v>0.02482573320254033</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>2.482581715253174</v>
+        <v>2.482573320254033</v>
       </c>
     </row>
     <row r="111">
